--- a/Research Assets/Engagement Metrics/Nigeria/twitter post engagement.xlsx
+++ b/Research Assets/Engagement Metrics/Nigeria/twitter post engagement.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1027" uniqueCount="724">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="521">
   <si>
     <t>tweet_id</t>
   </si>
@@ -50,615 +50,6 @@
   </si>
   <si>
     <t>error</t>
-  </si>
-  <si>
-    <t>1862512830987346178</t>
-  </si>
-  <si>
-    <t>1848028499606380555</t>
-  </si>
-  <si>
-    <t>1846206865396347176</t>
-  </si>
-  <si>
-    <t>1694030169491538367</t>
-  </si>
-  <si>
-    <t>1674519625365876736</t>
-  </si>
-  <si>
-    <t>1660336229508870151</t>
-  </si>
-  <si>
-    <t>1640650926959599618</t>
-  </si>
-  <si>
-    <t>1640369752345288706</t>
-  </si>
-  <si>
-    <t>1612001517711523841</t>
-  </si>
-  <si>
-    <t>1226450923859464193</t>
-  </si>
-  <si>
-    <t>1226493015319105537</t>
-  </si>
-  <si>
-    <t>1309190324355563521</t>
-  </si>
-  <si>
-    <t>1309679015171698690</t>
-  </si>
-  <si>
-    <t>1333661251948441600</t>
-  </si>
-  <si>
-    <t>1396817067316289537</t>
-  </si>
-  <si>
-    <t>1396816102240489479</t>
-  </si>
-  <si>
-    <t>1484112712443518978</t>
-  </si>
-  <si>
-    <t>1558235509062770688</t>
-  </si>
-  <si>
-    <t>1557661960992428032</t>
-  </si>
-  <si>
-    <t>1852709730671636910</t>
-  </si>
-  <si>
-    <t>1901981220218577289</t>
-  </si>
-  <si>
-    <t>1991944018058727780</t>
-  </si>
-  <si>
-    <t>1594672742464622592</t>
-  </si>
-  <si>
-    <t>1380908200388661256</t>
-  </si>
-  <si>
-    <t>1223908274380079107</t>
-  </si>
-  <si>
-    <t>1606029138787151873</t>
-  </si>
-  <si>
-    <t>1664024839475335168</t>
-  </si>
-  <si>
-    <t>1664019236597932032</t>
-  </si>
-  <si>
-    <t>1663625331905904641</t>
-  </si>
-  <si>
-    <t>1662863528896745472</t>
-  </si>
-  <si>
-    <t>1662499938104754176</t>
-  </si>
-  <si>
-    <t>1662402106442104832</t>
-  </si>
-  <si>
-    <t>1662139482320125979</t>
-  </si>
-  <si>
-    <t>1661717784420655104</t>
-  </si>
-  <si>
-    <t>1661677741761089540</t>
-  </si>
-  <si>
-    <t>1652790345598418944</t>
-  </si>
-  <si>
-    <t>1652785564301635587</t>
-  </si>
-  <si>
-    <t>1652627388813959168</t>
-  </si>
-  <si>
-    <t>1652263110000926720</t>
-  </si>
-  <si>
-    <t>1652003604738220032</t>
-  </si>
-  <si>
-    <t>1652003600707534862</t>
-  </si>
-  <si>
-    <t>1652003596555173910</t>
-  </si>
-  <si>
-    <t>1652003592700608534</t>
-  </si>
-  <si>
-    <t>1652003588904828930</t>
-  </si>
-  <si>
-    <t>1652003585423491082</t>
-  </si>
-  <si>
-    <t>1651950305637027840</t>
-  </si>
-  <si>
-    <t>1651922915389059073</t>
-  </si>
-  <si>
-    <t>1651920790151995392</t>
-  </si>
-  <si>
-    <t>1651911094334550016</t>
-  </si>
-  <si>
-    <t>1651564511965454342</t>
-  </si>
-  <si>
-    <t>1651213879349747712</t>
-  </si>
-  <si>
-    <t>1651167539420954624</t>
-  </si>
-  <si>
-    <t>1651167535662788610</t>
-  </si>
-  <si>
-    <t>1651167532152246280</t>
-  </si>
-  <si>
-    <t>1651167528620630016</t>
-  </si>
-  <si>
-    <t>1651167524862451713</t>
-  </si>
-  <si>
-    <t>1651167521314156544</t>
-  </si>
-  <si>
-    <t>1651167515811233795</t>
-  </si>
-  <si>
-    <t>1651167509154807810</t>
-  </si>
-  <si>
-    <t>1650962741857775634</t>
-  </si>
-  <si>
-    <t>1641505314150162433</t>
-  </si>
-  <si>
-    <t>1641439108915425280</t>
-  </si>
-  <si>
-    <t>1641094628173643778</t>
-  </si>
-  <si>
-    <t>1641094150786367489</t>
-  </si>
-  <si>
-    <t>1641089707684536320</t>
-  </si>
-  <si>
-    <t>1640845160861908993</t>
-  </si>
-  <si>
-    <t>1640435905209966597</t>
-  </si>
-  <si>
-    <t>1628468754609831944</t>
-  </si>
-  <si>
-    <t>1628463098209177603</t>
-  </si>
-  <si>
-    <t>1628416830455877634</t>
-  </si>
-  <si>
-    <t>1628416198659526656</t>
-  </si>
-  <si>
-    <t>1628159921660256256</t>
-  </si>
-  <si>
-    <t>1662051837590077440</t>
-  </si>
-  <si>
-    <t>1650853184552980485</t>
-  </si>
-  <si>
-    <t>1641175498410672130</t>
-  </si>
-  <si>
-    <t>1628509804153929742</t>
-  </si>
-  <si>
-    <t>1628469143472144385</t>
-  </si>
-  <si>
-    <t>1628156373774090243</t>
-  </si>
-  <si>
-    <t>1627968217946759170</t>
-  </si>
-  <si>
-    <t>1627951140041097218</t>
-  </si>
-  <si>
-    <t>1627951136610086912</t>
-  </si>
-  <si>
-    <t>1627951132671606784</t>
-  </si>
-  <si>
-    <t>1627942731166150657</t>
-  </si>
-  <si>
-    <t>1627942727752069120</t>
-  </si>
-  <si>
-    <t>1627942720940433413</t>
-  </si>
-  <si>
-    <t>1627942717320843271</t>
-  </si>
-  <si>
-    <t>1627281039818207234</t>
-  </si>
-  <si>
-    <t>1620475128575569921</t>
-  </si>
-  <si>
-    <t>1620466505115893760</t>
-  </si>
-  <si>
-    <t>1620386661296381955</t>
-  </si>
-  <si>
-    <t>1620377121280659459</t>
-  </si>
-  <si>
-    <t>1620034619918921734</t>
-  </si>
-  <si>
-    <t>1619354933362569220</t>
-  </si>
-  <si>
-    <t>1619000891243372544</t>
-  </si>
-  <si>
-    <t>1618655300382511105</t>
-  </si>
-  <si>
-    <t>1618258019317604355</t>
-  </si>
-  <si>
-    <t>1618256715186831361</t>
-  </si>
-  <si>
-    <t>1618239180903174149</t>
-  </si>
-  <si>
-    <t>1686113646470901760</t>
-  </si>
-  <si>
-    <t>1686081505393553408</t>
-  </si>
-  <si>
-    <t>1674877960300511234</t>
-  </si>
-  <si>
-    <t>1674876125061816321</t>
-  </si>
-  <si>
-    <t>1674869498929635350</t>
-  </si>
-  <si>
-    <t>1674856675990200329</t>
-  </si>
-  <si>
-    <t>1674854532285620224</t>
-  </si>
-  <si>
-    <t>1664013082002092033</t>
-  </si>
-  <si>
-    <t>1663979405817856006</t>
-  </si>
-  <si>
-    <t>1663974406429843456</t>
-  </si>
-  <si>
-    <t>1663973546870095875</t>
-  </si>
-  <si>
-    <t>1663872465410334720</t>
-  </si>
-  <si>
-    <t>1663830983601266688</t>
-  </si>
-  <si>
-    <t>1663822494107590656</t>
-  </si>
-  <si>
-    <t>1663818948503060480</t>
-  </si>
-  <si>
-    <t>1663801008604995584</t>
-  </si>
-  <si>
-    <t>1663628568440582147</t>
-  </si>
-  <si>
-    <t>1663626533565497346</t>
-  </si>
-  <si>
-    <t>1652779124778315777</t>
-  </si>
-  <si>
-    <t>1652761869009010688</t>
-  </si>
-  <si>
-    <t>1652759441123553280</t>
-  </si>
-  <si>
-    <t>1652752531469004802</t>
-  </si>
-  <si>
-    <t>1652668333668327426</t>
-  </si>
-  <si>
-    <t>1652592217830174722</t>
-  </si>
-  <si>
-    <t>1641321315909922816</t>
-  </si>
-  <si>
-    <t>1641315964141682688</t>
-  </si>
-  <si>
-    <t>1641174459674402816</t>
-  </si>
-  <si>
-    <t>1641155860255653914</t>
-  </si>
-  <si>
-    <t>1641047468832968706</t>
-  </si>
-  <si>
-    <t>1620540014445858817</t>
-  </si>
-  <si>
-    <t>1620530919324123136</t>
-  </si>
-  <si>
-    <t>1620526658288754688</t>
-  </si>
-  <si>
-    <t>1620496527683899392</t>
-  </si>
-  <si>
-    <t>1620469226896248832</t>
-  </si>
-  <si>
-    <t>1620401683191992324</t>
-  </si>
-  <si>
-    <t>1620368805393465344</t>
-  </si>
-  <si>
-    <t>1620328531157991429</t>
-  </si>
-  <si>
-    <t>1641155845353291780</t>
-  </si>
-  <si>
-    <t>1641155820632043521</t>
-  </si>
-  <si>
-    <t>1641097671443087360</t>
-  </si>
-  <si>
-    <t>1641087676420960258</t>
-  </si>
-  <si>
-    <t>1620368773386756096</t>
-  </si>
-  <si>
-    <t>1620368770975006721</t>
-  </si>
-  <si>
-    <t>1620340976228388867</t>
-  </si>
-  <si>
-    <t>1663996285093834754</t>
-  </si>
-  <si>
-    <t>1663996251531014145</t>
-  </si>
-  <si>
-    <t>1663996245789089794</t>
-  </si>
-  <si>
-    <t>1663980911627517962</t>
-  </si>
-  <si>
-    <t>1663979994899464203</t>
-  </si>
-  <si>
-    <t>1663976426515644417</t>
-  </si>
-  <si>
-    <t>1663974891501105152</t>
-  </si>
-  <si>
-    <t>1641155849115582478</t>
-  </si>
-  <si>
-    <t>1664054075162341376</t>
-  </si>
-  <si>
-    <t>1664050449861734417</t>
-  </si>
-  <si>
-    <t>1664045875650330626</t>
-  </si>
-  <si>
-    <t>1664023601756897280</t>
-  </si>
-  <si>
-    <t>1663879826623610881</t>
-  </si>
-  <si>
-    <t>1663878777707847682</t>
-  </si>
-  <si>
-    <t>1663864642567917569</t>
-  </si>
-  <si>
-    <t>1663863231159345154</t>
-  </si>
-  <si>
-    <t>1663849151526850561</t>
-  </si>
-  <si>
-    <t>1663681443803930624</t>
-  </si>
-  <si>
-    <t>1652792458181263360</t>
-  </si>
-  <si>
-    <t>1652789430443180032</t>
-  </si>
-  <si>
-    <t>1652786591478194176</t>
-  </si>
-  <si>
-    <t>1652778262702039048</t>
-  </si>
-  <si>
-    <t>1652775309014446081</t>
-  </si>
-  <si>
-    <t>1652759568479588352</t>
-  </si>
-  <si>
-    <t>1652758073541292032</t>
-  </si>
-  <si>
-    <t>1652730128177278980</t>
-  </si>
-  <si>
-    <t>1652653921628823554</t>
-  </si>
-  <si>
-    <t>1652637832043790337</t>
-  </si>
-  <si>
-    <t>1652632250100350977</t>
-  </si>
-  <si>
-    <t>1652613708361736194</t>
-  </si>
-  <si>
-    <t>1652613172400988160</t>
-  </si>
-  <si>
-    <t>1652611840378126336</t>
-  </si>
-  <si>
-    <t>1652610742292561921</t>
-  </si>
-  <si>
-    <t>1652610743580217344</t>
-  </si>
-  <si>
-    <t>1652607935829123072</t>
-  </si>
-  <si>
-    <t>1652606997215182850</t>
-  </si>
-  <si>
-    <t>1652605299235119104</t>
-  </si>
-  <si>
-    <t>1652604814889570304</t>
-  </si>
-  <si>
-    <t>1652603868771938306</t>
-  </si>
-  <si>
-    <t>1652600422668828672</t>
-  </si>
-  <si>
-    <t>1652597521510744064</t>
-  </si>
-  <si>
-    <t>1641887533855395854</t>
-  </si>
-  <si>
-    <t>1641855732931756033</t>
-  </si>
-  <si>
-    <t>1641800899814121474</t>
-  </si>
-  <si>
-    <t>1641792600863645696</t>
-  </si>
-  <si>
-    <t>1641787210054660097</t>
-  </si>
-  <si>
-    <t>1641780775753269248</t>
-  </si>
-  <si>
-    <t>1641780741360025602</t>
-  </si>
-  <si>
-    <t>1641776275877507073</t>
-  </si>
-  <si>
-    <t>1641760900993495041</t>
-  </si>
-  <si>
-    <t>1619650876221829121</t>
-  </si>
-  <si>
-    <t>1620358713474433024</t>
-  </si>
-  <si>
-    <t>1664037638863454208</t>
-  </si>
-  <si>
-    <t>1663858197310865409</t>
-  </si>
-  <si>
-    <t>1663852815511429120</t>
-  </si>
-  <si>
-    <t>1663817389069283328</t>
-  </si>
-  <si>
-    <t>1652613288054726657</t>
-  </si>
-  <si>
-    <t>1652599667190906881</t>
-  </si>
-  <si>
-    <t>1641796973115187205</t>
-  </si>
-  <si>
-    <t>1641778203978088448</t>
-  </si>
-  <si>
-    <t>1619731584768442368</t>
   </si>
   <si>
     <t>Deyemi Okanlawon</t>
@@ -2838,17 +2229,17 @@
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" t="s">
+      <c r="A2">
+        <v>1.862512830987346E+18</v>
+      </c>
+      <c r="B2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" t="s">
-        <v>215</v>
-      </c>
       <c r="C2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
         <v>219</v>
-      </c>
-      <c r="D2" t="s">
-        <v>422</v>
       </c>
       <c r="E2">
         <v>11</v>
@@ -2869,21 +2260,21 @@
         <v>575</v>
       </c>
       <c r="K2" t="s">
-        <v>573</v>
+        <v>370</v>
       </c>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" t="s">
-        <v>13</v>
+      <c r="A3">
+        <v>1.848028499606381E+18</v>
       </c>
       <c r="B3" t="s">
-        <v>215</v>
+        <v>12</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
         <v>220</v>
-      </c>
-      <c r="D3" t="s">
-        <v>423</v>
       </c>
       <c r="E3">
         <v>72</v>
@@ -2904,21 +2295,21 @@
         <v>3161</v>
       </c>
       <c r="K3" t="s">
-        <v>574</v>
+        <v>371</v>
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" t="s">
-        <v>14</v>
+      <c r="A4">
+        <v>1.846206865396347E+18</v>
       </c>
       <c r="B4" t="s">
-        <v>215</v>
+        <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
         <v>221</v>
-      </c>
-      <c r="D4" t="s">
-        <v>424</v>
       </c>
       <c r="E4">
         <v>54</v>
@@ -2939,21 +2330,21 @@
         <v>1417</v>
       </c>
       <c r="K4" t="s">
-        <v>575</v>
+        <v>372</v>
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" t="s">
-        <v>15</v>
+      <c r="A5">
+        <v>1.694030169491538E+18</v>
       </c>
       <c r="B5" t="s">
-        <v>215</v>
+        <v>12</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
         <v>222</v>
-      </c>
-      <c r="D5" t="s">
-        <v>425</v>
       </c>
       <c r="E5">
         <v>20</v>
@@ -2974,21 +2365,21 @@
         <v>1439</v>
       </c>
       <c r="K5" t="s">
-        <v>576</v>
+        <v>373</v>
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" t="s">
-        <v>16</v>
+      <c r="A6">
+        <v>1.674519625365877E+18</v>
       </c>
       <c r="B6" t="s">
-        <v>215</v>
+        <v>12</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" t="s">
         <v>223</v>
-      </c>
-      <c r="D6" t="s">
-        <v>426</v>
       </c>
       <c r="E6">
         <v>15</v>
@@ -3009,21 +2400,21 @@
         <v>1611</v>
       </c>
       <c r="K6" t="s">
-        <v>577</v>
+        <v>374</v>
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" t="s">
-        <v>17</v>
+      <c r="A7">
+        <v>1.66033622950887E+18</v>
       </c>
       <c r="B7" t="s">
-        <v>215</v>
+        <v>12</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" t="s">
         <v>224</v>
-      </c>
-      <c r="D7" t="s">
-        <v>427</v>
       </c>
       <c r="E7">
         <v>27</v>
@@ -3044,21 +2435,21 @@
         <v>1367</v>
       </c>
       <c r="K7" t="s">
-        <v>578</v>
+        <v>375</v>
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" t="s">
-        <v>18</v>
+      <c r="A8">
+        <v>1.6406509269596E+18</v>
       </c>
       <c r="B8" t="s">
-        <v>215</v>
+        <v>12</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" t="s">
         <v>225</v>
-      </c>
-      <c r="D8" t="s">
-        <v>428</v>
       </c>
       <c r="E8">
         <v>173</v>
@@ -3079,21 +2470,21 @@
         <v>10166</v>
       </c>
       <c r="K8" t="s">
-        <v>579</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" t="s">
-        <v>19</v>
+      <c r="A9">
+        <v>1.640369752345289E+18</v>
       </c>
       <c r="B9" t="s">
-        <v>215</v>
+        <v>12</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" t="s">
         <v>226</v>
-      </c>
-      <c r="D9" t="s">
-        <v>429</v>
       </c>
       <c r="E9">
         <v>111</v>
@@ -3114,21 +2505,21 @@
         <v>4927</v>
       </c>
       <c r="K9" t="s">
-        <v>580</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" t="s">
-        <v>20</v>
+      <c r="A10">
+        <v>1.612001517711524E+18</v>
       </c>
       <c r="B10" t="s">
-        <v>215</v>
+        <v>12</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" t="s">
         <v>227</v>
-      </c>
-      <c r="D10" t="s">
-        <v>430</v>
       </c>
       <c r="E10">
         <v>101</v>
@@ -3149,21 +2540,21 @@
         <v>4774</v>
       </c>
       <c r="K10" t="s">
-        <v>581</v>
+        <v>378</v>
       </c>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" t="s">
-        <v>21</v>
+      <c r="A11">
+        <v>1.226450923859464E+18</v>
       </c>
       <c r="B11" t="s">
-        <v>215</v>
+        <v>12</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" t="s">
         <v>228</v>
-      </c>
-      <c r="D11" t="s">
-        <v>431</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -3181,22 +2572,22 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>582</v>
+        <v>379</v>
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" t="s">
-        <v>22</v>
+      <c r="A12">
+        <v>1.226493015319106E+18</v>
       </c>
       <c r="B12" t="s">
-        <v>215</v>
+        <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" t="s">
         <v>229</v>
       </c>
-      <c r="D12" t="s">
-        <v>432</v>
-      </c>
       <c r="E12">
         <v>0</v>
       </c>
@@ -3213,21 +2604,21 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>583</v>
+        <v>380</v>
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" t="s">
-        <v>23</v>
+      <c r="A13">
+        <v>1.309190324355564E+18</v>
       </c>
       <c r="B13" t="s">
-        <v>215</v>
+        <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" t="s">
         <v>230</v>
-      </c>
-      <c r="D13" t="s">
-        <v>433</v>
       </c>
       <c r="E13">
         <v>104</v>
@@ -3245,24 +2636,24 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>584</v>
+        <v>381</v>
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" t="s">
-        <v>24</v>
+      <c r="A14">
+        <v>1.309679015171699E+18</v>
       </c>
       <c r="B14" t="s">
-        <v>215</v>
+        <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" t="s">
         <v>231</v>
       </c>
-      <c r="D14" t="s">
-        <v>434</v>
-      </c>
       <c r="E14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -3277,22 +2668,22 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>585</v>
+        <v>382</v>
       </c>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" t="s">
-        <v>25</v>
+      <c r="A15">
+        <v>1.333661251948442E+18</v>
       </c>
       <c r="B15" t="s">
-        <v>215</v>
+        <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" t="s">
         <v>232</v>
       </c>
-      <c r="D15" t="s">
-        <v>435</v>
-      </c>
       <c r="E15">
         <v>0</v>
       </c>
@@ -3309,30 +2700,30 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>586</v>
+        <v>383</v>
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" t="s">
-        <v>26</v>
+      <c r="A16">
+        <v>1.39681706731629E+18</v>
       </c>
       <c r="B16" t="s">
-        <v>215</v>
+        <v>12</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" t="s">
         <v>233</v>
       </c>
-      <c r="D16" t="s">
-        <v>436</v>
-      </c>
       <c r="E16">
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -3341,21 +2732,21 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>587</v>
+        <v>384</v>
       </c>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" t="s">
-        <v>27</v>
+      <c r="A17">
+        <v>1.396816102240489E+18</v>
       </c>
       <c r="B17" t="s">
-        <v>215</v>
+        <v>12</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>234</v>
+        <v>31</v>
       </c>
       <c r="D17" t="s">
-        <v>436</v>
+        <v>233</v>
       </c>
       <c r="E17">
         <v>163</v>
@@ -3373,21 +2764,21 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>587</v>
+        <v>384</v>
       </c>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" t="s">
-        <v>28</v>
+      <c r="A18">
+        <v>1.484112712443519E+18</v>
       </c>
       <c r="B18" t="s">
-        <v>215</v>
+        <v>12</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>235</v>
+        <v>32</v>
       </c>
       <c r="D18" t="s">
-        <v>437</v>
+        <v>234</v>
       </c>
       <c r="E18">
         <v>35</v>
@@ -3405,85 +2796,85 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>588</v>
+        <v>385</v>
       </c>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" t="s">
-        <v>29</v>
+      <c r="A19">
+        <v>1.558235509062771E+18</v>
       </c>
       <c r="B19" t="s">
-        <v>215</v>
+        <v>12</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" t="s">
+        <v>235</v>
+      </c>
+      <c r="E19">
+        <v>107</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="K19" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20">
+        <v>1.557661960992428E+18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" t="s">
+        <v>235</v>
+      </c>
+      <c r="E20">
+        <v>6246</v>
+      </c>
+      <c r="F20">
+        <v>2143</v>
+      </c>
+      <c r="G20">
+        <v>102</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="K20" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21">
+        <v>1.852709730671637E+18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" t="s">
         <v>236</v>
-      </c>
-      <c r="D19" t="s">
-        <v>438</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="K19" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" t="s">
-        <v>30</v>
-      </c>
-      <c r="B20" t="s">
-        <v>215</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="D20" t="s">
-        <v>438</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="K20" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" t="s">
-        <v>215</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="D21" t="s">
-        <v>439</v>
       </c>
       <c r="E21">
         <v>93</v>
@@ -3504,21 +2895,21 @@
         <v>4385</v>
       </c>
       <c r="K21" t="s">
-        <v>590</v>
+        <v>387</v>
       </c>
     </row>
     <row r="22" spans="1:11">
-      <c r="A22" t="s">
-        <v>32</v>
+      <c r="A22">
+        <v>1.901981220218577E+18</v>
       </c>
       <c r="B22" t="s">
-        <v>215</v>
+        <v>12</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>239</v>
+        <v>36</v>
       </c>
       <c r="D22" t="s">
-        <v>440</v>
+        <v>237</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -3539,21 +2930,21 @@
         <v>1607</v>
       </c>
       <c r="K22" t="s">
-        <v>591</v>
+        <v>388</v>
       </c>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" t="s">
-        <v>33</v>
+      <c r="A23">
+        <v>1.991944018058728E+18</v>
       </c>
       <c r="B23" t="s">
-        <v>215</v>
+        <v>12</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>240</v>
+        <v>37</v>
       </c>
       <c r="D23" t="s">
-        <v>441</v>
+        <v>238</v>
       </c>
       <c r="E23">
         <v>182</v>
@@ -3574,21 +2965,21 @@
         <v>5765</v>
       </c>
       <c r="K23" t="s">
-        <v>592</v>
+        <v>389</v>
       </c>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" t="s">
-        <v>34</v>
+      <c r="A24">
+        <v>1.594672742464623E+18</v>
       </c>
       <c r="B24" t="s">
-        <v>215</v>
+        <v>12</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>241</v>
+        <v>38</v>
       </c>
       <c r="D24" t="s">
-        <v>442</v>
+        <v>239</v>
       </c>
       <c r="E24">
         <v>228</v>
@@ -3606,21 +2997,21 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>593</v>
+        <v>390</v>
       </c>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" t="s">
-        <v>35</v>
+      <c r="A25">
+        <v>1.380908200388661E+18</v>
       </c>
       <c r="B25" t="s">
-        <v>215</v>
+        <v>12</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>242</v>
+        <v>39</v>
       </c>
       <c r="D25" t="s">
-        <v>443</v>
+        <v>240</v>
       </c>
       <c r="E25">
         <v>30</v>
@@ -3638,21 +3029,21 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>594</v>
+        <v>391</v>
       </c>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" t="s">
-        <v>36</v>
+      <c r="A26">
+        <v>1.223908274380079E+18</v>
       </c>
       <c r="B26" t="s">
-        <v>215</v>
+        <v>12</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>243</v>
+        <v>40</v>
       </c>
       <c r="D26" t="s">
-        <v>444</v>
+        <v>241</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -3670,21 +3061,21 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>595</v>
+        <v>392</v>
       </c>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" t="s">
-        <v>37</v>
+      <c r="A27">
+        <v>1.606029138787152E+18</v>
       </c>
       <c r="B27" t="s">
-        <v>215</v>
+        <v>12</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>244</v>
+        <v>41</v>
       </c>
       <c r="D27" t="s">
-        <v>445</v>
+        <v>242</v>
       </c>
       <c r="E27">
         <v>44</v>
@@ -3705,21 +3096,21 @@
         <v>3201</v>
       </c>
       <c r="K27" t="s">
-        <v>596</v>
+        <v>393</v>
       </c>
     </row>
     <row r="28" spans="1:11">
-      <c r="A28" t="s">
-        <v>38</v>
+      <c r="A28">
+        <v>1.664024839475335E+18</v>
       </c>
       <c r="B28" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>245</v>
+        <v>42</v>
       </c>
       <c r="D28" t="s">
-        <v>446</v>
+        <v>243</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -3740,24 +3131,24 @@
         <v>353324</v>
       </c>
       <c r="K28" t="s">
-        <v>597</v>
+        <v>394</v>
       </c>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" t="s">
-        <v>39</v>
+      <c r="A29">
+        <v>1.664019236597932E+18</v>
       </c>
       <c r="B29" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>246</v>
+        <v>43</v>
       </c>
       <c r="D29" t="s">
-        <v>446</v>
+        <v>243</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>7596</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -3775,21 +3166,21 @@
         <v>353324</v>
       </c>
       <c r="K29" t="s">
-        <v>597</v>
+        <v>394</v>
       </c>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" t="s">
-        <v>40</v>
+      <c r="A30">
+        <v>1.663625331905905E+18</v>
       </c>
       <c r="B30" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>247</v>
+        <v>44</v>
       </c>
       <c r="D30" t="s">
-        <v>447</v>
+        <v>244</v>
       </c>
       <c r="E30">
         <v>4409</v>
@@ -3810,24 +3201,24 @@
         <v>283804</v>
       </c>
       <c r="K30" t="s">
-        <v>598</v>
+        <v>395</v>
       </c>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" t="s">
-        <v>41</v>
+      <c r="A31">
+        <v>1.662863528896745E+18</v>
       </c>
       <c r="B31" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="D31" t="s">
-        <v>448</v>
+        <v>245</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>9842</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -3845,24 +3236,24 @@
         <v>610428</v>
       </c>
       <c r="K31" t="s">
-        <v>599</v>
+        <v>396</v>
       </c>
     </row>
     <row r="32" spans="1:11">
-      <c r="A32" t="s">
-        <v>42</v>
+      <c r="A32">
+        <v>1.662499938104754E+18</v>
       </c>
       <c r="B32" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>249</v>
+        <v>46</v>
       </c>
       <c r="D32" t="s">
-        <v>449</v>
+        <v>246</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>2369</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -3880,21 +3271,21 @@
         <v>106744</v>
       </c>
       <c r="K32" t="s">
-        <v>600</v>
+        <v>397</v>
       </c>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" t="s">
-        <v>43</v>
+      <c r="A33">
+        <v>1.662402106442105E+18</v>
       </c>
       <c r="B33" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>250</v>
+        <v>47</v>
       </c>
       <c r="D33" t="s">
-        <v>450</v>
+        <v>247</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -3915,24 +3306,24 @@
         <v>242568</v>
       </c>
       <c r="K33" t="s">
-        <v>601</v>
+        <v>398</v>
       </c>
     </row>
     <row r="34" spans="1:11">
-      <c r="A34" t="s">
-        <v>44</v>
+      <c r="A34">
+        <v>1.662139482320126E+18</v>
       </c>
       <c r="B34" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>251</v>
+        <v>48</v>
       </c>
       <c r="D34" t="s">
-        <v>451</v>
+        <v>248</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>4312</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -3950,21 +3341,21 @@
         <v>199925</v>
       </c>
       <c r="K34" t="s">
-        <v>602</v>
+        <v>399</v>
       </c>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" t="s">
-        <v>45</v>
+      <c r="A35">
+        <v>1.661717784420655E+18</v>
       </c>
       <c r="B35" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>252</v>
+        <v>49</v>
       </c>
       <c r="D35" t="s">
-        <v>452</v>
+        <v>249</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -3985,21 +3376,21 @@
         <v>130837</v>
       </c>
       <c r="K35" t="s">
-        <v>603</v>
+        <v>400</v>
       </c>
     </row>
     <row r="36" spans="1:11">
-      <c r="A36" t="s">
-        <v>46</v>
+      <c r="A36">
+        <v>1.66167774176109E+18</v>
       </c>
       <c r="B36" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>253</v>
+        <v>50</v>
       </c>
       <c r="D36" t="s">
-        <v>453</v>
+        <v>250</v>
       </c>
       <c r="E36">
         <v>6853</v>
@@ -4020,30 +3411,30 @@
         <v>284181</v>
       </c>
       <c r="K36" t="s">
-        <v>604</v>
+        <v>401</v>
       </c>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" t="s">
-        <v>47</v>
+      <c r="A37">
+        <v>1.652790345598419E+18</v>
       </c>
       <c r="B37" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>254</v>
+        <v>51</v>
       </c>
       <c r="D37" t="s">
-        <v>454</v>
+        <v>251</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>3780</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>574</v>
       </c>
       <c r="H37">
         <v>0</v>
@@ -4055,21 +3446,21 @@
         <v>353008</v>
       </c>
       <c r="K37" t="s">
-        <v>605</v>
+        <v>402</v>
       </c>
     </row>
     <row r="38" spans="1:11">
-      <c r="A38" t="s">
-        <v>48</v>
+      <c r="A38">
+        <v>1.652785564301636E+18</v>
       </c>
       <c r="B38" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>255</v>
+        <v>52</v>
       </c>
       <c r="D38" t="s">
-        <v>454</v>
+        <v>251</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -4090,21 +3481,21 @@
         <v>353008</v>
       </c>
       <c r="K38" t="s">
-        <v>605</v>
+        <v>402</v>
       </c>
     </row>
     <row r="39" spans="1:11">
-      <c r="A39" t="s">
-        <v>49</v>
+      <c r="A39">
+        <v>1.652627388813959E+18</v>
       </c>
       <c r="B39" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>256</v>
+        <v>53</v>
       </c>
       <c r="D39" t="s">
-        <v>455</v>
+        <v>252</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -4125,21 +3516,21 @@
         <v>257616</v>
       </c>
       <c r="K39" t="s">
-        <v>606</v>
+        <v>403</v>
       </c>
     </row>
     <row r="40" spans="1:11">
-      <c r="A40" t="s">
-        <v>50</v>
+      <c r="A40">
+        <v>1.652263110000927E+18</v>
       </c>
       <c r="B40" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>257</v>
+        <v>54</v>
       </c>
       <c r="D40" t="s">
-        <v>456</v>
+        <v>253</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -4160,21 +3551,21 @@
         <v>114198</v>
       </c>
       <c r="K40" t="s">
-        <v>607</v>
+        <v>404</v>
       </c>
     </row>
     <row r="41" spans="1:11">
-      <c r="A41" t="s">
-        <v>51</v>
+      <c r="A41">
+        <v>1.65200360473822E+18</v>
       </c>
       <c r="B41" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>258</v>
+        <v>55</v>
       </c>
       <c r="D41" t="s">
-        <v>457</v>
+        <v>254</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -4195,21 +3586,21 @@
         <v>290755</v>
       </c>
       <c r="K41" t="s">
-        <v>608</v>
+        <v>405</v>
       </c>
     </row>
     <row r="42" spans="1:11">
-      <c r="A42" t="s">
-        <v>52</v>
+      <c r="A42">
+        <v>1.652003600707535E+18</v>
       </c>
       <c r="B42" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>259</v>
+        <v>56</v>
       </c>
       <c r="D42" t="s">
-        <v>457</v>
+        <v>254</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -4230,21 +3621,21 @@
         <v>290755</v>
       </c>
       <c r="K42" t="s">
-        <v>608</v>
+        <v>405</v>
       </c>
     </row>
     <row r="43" spans="1:11">
-      <c r="A43" t="s">
-        <v>53</v>
+      <c r="A43">
+        <v>1.652003596555174E+18</v>
       </c>
       <c r="B43" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>260</v>
+        <v>57</v>
       </c>
       <c r="D43" t="s">
-        <v>457</v>
+        <v>254</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -4265,21 +3656,21 @@
         <v>290755</v>
       </c>
       <c r="K43" t="s">
-        <v>608</v>
+        <v>405</v>
       </c>
     </row>
     <row r="44" spans="1:11">
-      <c r="A44" t="s">
-        <v>54</v>
+      <c r="A44">
+        <v>1.652003592700609E+18</v>
       </c>
       <c r="B44" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>261</v>
+        <v>58</v>
       </c>
       <c r="D44" t="s">
-        <v>457</v>
+        <v>254</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -4300,21 +3691,21 @@
         <v>290755</v>
       </c>
       <c r="K44" t="s">
-        <v>608</v>
+        <v>405</v>
       </c>
     </row>
     <row r="45" spans="1:11">
-      <c r="A45" t="s">
-        <v>55</v>
+      <c r="A45">
+        <v>1.652003588904829E+18</v>
       </c>
       <c r="B45" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>262</v>
+        <v>59</v>
       </c>
       <c r="D45" t="s">
-        <v>457</v>
+        <v>254</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -4335,21 +3726,21 @@
         <v>290755</v>
       </c>
       <c r="K45" t="s">
-        <v>608</v>
+        <v>405</v>
       </c>
     </row>
     <row r="46" spans="1:11">
-      <c r="A46" t="s">
-        <v>56</v>
+      <c r="A46">
+        <v>1.652003585423491E+18</v>
       </c>
       <c r="B46" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>263</v>
+        <v>60</v>
       </c>
       <c r="D46" t="s">
-        <v>457</v>
+        <v>254</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -4370,21 +3761,21 @@
         <v>290755</v>
       </c>
       <c r="K46" t="s">
-        <v>608</v>
+        <v>405</v>
       </c>
     </row>
     <row r="47" spans="1:11">
-      <c r="A47" t="s">
-        <v>57</v>
+      <c r="A47">
+        <v>1.651950305637028E+18</v>
       </c>
       <c r="B47" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>264</v>
+        <v>61</v>
       </c>
       <c r="D47" t="s">
-        <v>458</v>
+        <v>255</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -4405,21 +3796,21 @@
         <v>110425</v>
       </c>
       <c r="K47" t="s">
-        <v>609</v>
+        <v>406</v>
       </c>
     </row>
     <row r="48" spans="1:11">
-      <c r="A48" t="s">
-        <v>58</v>
+      <c r="A48">
+        <v>1.651922915389059E+18</v>
       </c>
       <c r="B48" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>265</v>
+        <v>62</v>
       </c>
       <c r="D48" t="s">
-        <v>459</v>
+        <v>256</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -4440,21 +3831,21 @@
         <v>222855</v>
       </c>
       <c r="K48" t="s">
-        <v>610</v>
+        <v>407</v>
       </c>
     </row>
     <row r="49" spans="1:11">
-      <c r="A49" t="s">
-        <v>59</v>
+      <c r="A49">
+        <v>1.651920790151995E+18</v>
       </c>
       <c r="B49" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>266</v>
+        <v>63</v>
       </c>
       <c r="D49" t="s">
-        <v>459</v>
+        <v>256</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -4475,21 +3866,21 @@
         <v>222855</v>
       </c>
       <c r="K49" t="s">
-        <v>610</v>
+        <v>407</v>
       </c>
     </row>
     <row r="50" spans="1:11">
-      <c r="A50" t="s">
-        <v>60</v>
+      <c r="A50">
+        <v>1.65191109433455E+18</v>
       </c>
       <c r="B50" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>267</v>
+        <v>64</v>
       </c>
       <c r="D50" t="s">
-        <v>460</v>
+        <v>257</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -4510,21 +3901,21 @@
         <v>33158</v>
       </c>
       <c r="K50" t="s">
-        <v>611</v>
+        <v>408</v>
       </c>
     </row>
     <row r="51" spans="1:11">
-      <c r="A51" t="s">
-        <v>61</v>
+      <c r="A51">
+        <v>1.651564511965454E+18</v>
       </c>
       <c r="B51" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>268</v>
+        <v>65</v>
       </c>
       <c r="D51" t="s">
-        <v>461</v>
+        <v>258</v>
       </c>
       <c r="E51">
         <v>9170</v>
@@ -4545,30 +3936,30 @@
         <v>523350</v>
       </c>
       <c r="K51" t="s">
-        <v>612</v>
+        <v>409</v>
       </c>
     </row>
     <row r="52" spans="1:11">
-      <c r="A52" t="s">
-        <v>62</v>
+      <c r="A52">
+        <v>1.651213879349748E+18</v>
       </c>
       <c r="B52" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>269</v>
+        <v>66</v>
       </c>
       <c r="D52" t="s">
-        <v>462</v>
+        <v>259</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>7524</v>
       </c>
       <c r="F52">
-        <v>0</v>
+        <v>974</v>
       </c>
       <c r="G52">
-        <v>0</v>
+        <v>848</v>
       </c>
       <c r="H52">
         <v>0</v>
@@ -4580,21 +3971,21 @@
         <v>1018516</v>
       </c>
       <c r="K52" t="s">
-        <v>613</v>
+        <v>410</v>
       </c>
     </row>
     <row r="53" spans="1:11">
-      <c r="A53" t="s">
-        <v>63</v>
+      <c r="A53">
+        <v>1.651167539420955E+18</v>
       </c>
       <c r="B53" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>270</v>
+        <v>67</v>
       </c>
       <c r="D53" t="s">
-        <v>463</v>
+        <v>260</v>
       </c>
       <c r="E53">
         <v>4426</v>
@@ -4615,21 +4006,21 @@
         <v>436351</v>
       </c>
       <c r="K53" t="s">
-        <v>614</v>
+        <v>411</v>
       </c>
     </row>
     <row r="54" spans="1:11">
-      <c r="A54" t="s">
-        <v>64</v>
+      <c r="A54">
+        <v>1.651167535662789E+18</v>
       </c>
       <c r="B54" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>271</v>
+        <v>68</v>
       </c>
       <c r="D54" t="s">
-        <v>463</v>
+        <v>260</v>
       </c>
       <c r="E54">
         <v>4426</v>
@@ -4650,21 +4041,21 @@
         <v>436351</v>
       </c>
       <c r="K54" t="s">
-        <v>614</v>
+        <v>411</v>
       </c>
     </row>
     <row r="55" spans="1:11">
-      <c r="A55" t="s">
-        <v>65</v>
+      <c r="A55">
+        <v>1.651167532152246E+18</v>
       </c>
       <c r="B55" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>272</v>
+        <v>69</v>
       </c>
       <c r="D55" t="s">
-        <v>463</v>
+        <v>260</v>
       </c>
       <c r="E55">
         <v>4426</v>
@@ -4685,21 +4076,21 @@
         <v>436351</v>
       </c>
       <c r="K55" t="s">
-        <v>614</v>
+        <v>411</v>
       </c>
     </row>
     <row r="56" spans="1:11">
-      <c r="A56" t="s">
-        <v>66</v>
+      <c r="A56">
+        <v>1.65116752862063E+18</v>
       </c>
       <c r="B56" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>273</v>
+        <v>70</v>
       </c>
       <c r="D56" t="s">
-        <v>463</v>
+        <v>260</v>
       </c>
       <c r="E56">
         <v>4426</v>
@@ -4720,21 +4111,21 @@
         <v>436351</v>
       </c>
       <c r="K56" t="s">
-        <v>614</v>
+        <v>411</v>
       </c>
     </row>
     <row r="57" spans="1:11">
-      <c r="A57" t="s">
-        <v>67</v>
+      <c r="A57">
+        <v>1.651167524862452E+18</v>
       </c>
       <c r="B57" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>274</v>
+        <v>71</v>
       </c>
       <c r="D57" t="s">
-        <v>463</v>
+        <v>260</v>
       </c>
       <c r="E57">
         <v>4426</v>
@@ -4755,21 +4146,21 @@
         <v>436351</v>
       </c>
       <c r="K57" t="s">
-        <v>614</v>
+        <v>411</v>
       </c>
     </row>
     <row r="58" spans="1:11">
-      <c r="A58" t="s">
-        <v>68</v>
+      <c r="A58">
+        <v>1.651167521314157E+18</v>
       </c>
       <c r="B58" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>275</v>
+        <v>72</v>
       </c>
       <c r="D58" t="s">
-        <v>463</v>
+        <v>260</v>
       </c>
       <c r="E58">
         <v>4426</v>
@@ -4790,21 +4181,21 @@
         <v>436351</v>
       </c>
       <c r="K58" t="s">
-        <v>614</v>
+        <v>411</v>
       </c>
     </row>
     <row r="59" spans="1:11">
-      <c r="A59" t="s">
-        <v>69</v>
+      <c r="A59">
+        <v>1.651167515811234E+18</v>
       </c>
       <c r="B59" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>276</v>
+        <v>73</v>
       </c>
       <c r="D59" t="s">
-        <v>463</v>
+        <v>260</v>
       </c>
       <c r="E59">
         <v>4426</v>
@@ -4825,21 +4216,21 @@
         <v>436351</v>
       </c>
       <c r="K59" t="s">
-        <v>614</v>
+        <v>411</v>
       </c>
     </row>
     <row r="60" spans="1:11">
-      <c r="A60" t="s">
-        <v>70</v>
+      <c r="A60">
+        <v>1.651167509154808E+18</v>
       </c>
       <c r="B60" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>277</v>
+        <v>74</v>
       </c>
       <c r="D60" t="s">
-        <v>463</v>
+        <v>260</v>
       </c>
       <c r="E60">
         <v>4426</v>
@@ -4860,21 +4251,21 @@
         <v>436351</v>
       </c>
       <c r="K60" t="s">
-        <v>614</v>
+        <v>411</v>
       </c>
     </row>
     <row r="61" spans="1:11">
-      <c r="A61" t="s">
-        <v>71</v>
+      <c r="A61">
+        <v>1.650962741857776E+18</v>
       </c>
       <c r="B61" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>278</v>
+        <v>75</v>
       </c>
       <c r="D61" t="s">
-        <v>464</v>
+        <v>261</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -4895,21 +4286,21 @@
         <v>289209</v>
       </c>
       <c r="K61" t="s">
-        <v>615</v>
+        <v>412</v>
       </c>
     </row>
     <row r="62" spans="1:11">
-      <c r="A62" t="s">
-        <v>72</v>
+      <c r="A62">
+        <v>1.641505314150162E+18</v>
       </c>
       <c r="B62" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>279</v>
+        <v>76</v>
       </c>
       <c r="D62" t="s">
-        <v>465</v>
+        <v>262</v>
       </c>
       <c r="E62">
         <v>3007</v>
@@ -4930,21 +4321,21 @@
         <v>306182</v>
       </c>
       <c r="K62" t="s">
-        <v>616</v>
+        <v>413</v>
       </c>
     </row>
     <row r="63" spans="1:11">
-      <c r="A63" t="s">
-        <v>73</v>
+      <c r="A63">
+        <v>1.641439108915425E+18</v>
       </c>
       <c r="B63" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>280</v>
+        <v>77</v>
       </c>
       <c r="D63" t="s">
-        <v>466</v>
+        <v>263</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -4965,21 +4356,21 @@
         <v>127474</v>
       </c>
       <c r="K63" t="s">
-        <v>617</v>
+        <v>414</v>
       </c>
     </row>
     <row r="64" spans="1:11">
-      <c r="A64" t="s">
-        <v>74</v>
+      <c r="A64">
+        <v>1.641094628173644E+18</v>
       </c>
       <c r="B64" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>281</v>
+        <v>78</v>
       </c>
       <c r="D64" t="s">
-        <v>467</v>
+        <v>264</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -5000,21 +4391,21 @@
         <v>225907</v>
       </c>
       <c r="K64" t="s">
-        <v>618</v>
+        <v>415</v>
       </c>
     </row>
     <row r="65" spans="1:11">
-      <c r="A65" t="s">
-        <v>75</v>
+      <c r="A65">
+        <v>1.641094150786367E+18</v>
       </c>
       <c r="B65" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>282</v>
+        <v>79</v>
       </c>
       <c r="D65" t="s">
-        <v>467</v>
+        <v>264</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -5035,21 +4426,21 @@
         <v>225907</v>
       </c>
       <c r="K65" t="s">
-        <v>618</v>
+        <v>415</v>
       </c>
     </row>
     <row r="66" spans="1:11">
-      <c r="A66" t="s">
-        <v>76</v>
+      <c r="A66">
+        <v>1.641089707684536E+18</v>
       </c>
       <c r="B66" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>283</v>
+        <v>80</v>
       </c>
       <c r="D66" t="s">
-        <v>468</v>
+        <v>265</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -5070,21 +4461,21 @@
         <v>72451</v>
       </c>
       <c r="K66" t="s">
-        <v>619</v>
+        <v>416</v>
       </c>
     </row>
     <row r="67" spans="1:11">
-      <c r="A67" t="s">
-        <v>77</v>
+      <c r="A67">
+        <v>1.640845160861909E+18</v>
       </c>
       <c r="B67" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>284</v>
+        <v>81</v>
       </c>
       <c r="D67" t="s">
-        <v>469</v>
+        <v>266</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -5105,21 +4496,21 @@
         <v>2778</v>
       </c>
       <c r="K67" t="s">
-        <v>620</v>
+        <v>417</v>
       </c>
     </row>
     <row r="68" spans="1:11">
-      <c r="A68" t="s">
-        <v>78</v>
+      <c r="A68">
+        <v>1.640435905209967E+18</v>
       </c>
       <c r="B68" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>285</v>
+        <v>82</v>
       </c>
       <c r="D68" t="s">
-        <v>470</v>
+        <v>267</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -5140,21 +4531,21 @@
         <v>76948</v>
       </c>
       <c r="K68" t="s">
-        <v>621</v>
+        <v>418</v>
       </c>
     </row>
     <row r="69" spans="1:11">
-      <c r="A69" t="s">
-        <v>79</v>
+      <c r="A69">
+        <v>1.628468754609832E+18</v>
       </c>
       <c r="B69" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>286</v>
+        <v>83</v>
       </c>
       <c r="D69" t="s">
-        <v>471</v>
+        <v>268</v>
       </c>
       <c r="E69">
         <v>3195</v>
@@ -5175,21 +4566,21 @@
         <v>353004</v>
       </c>
       <c r="K69" t="s">
-        <v>622</v>
+        <v>419</v>
       </c>
     </row>
     <row r="70" spans="1:11">
-      <c r="A70" t="s">
-        <v>80</v>
+      <c r="A70">
+        <v>1.628463098209178E+18</v>
       </c>
       <c r="B70" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>287</v>
+        <v>84</v>
       </c>
       <c r="D70" t="s">
-        <v>471</v>
+        <v>268</v>
       </c>
       <c r="E70">
         <v>3195</v>
@@ -5210,21 +4601,21 @@
         <v>353004</v>
       </c>
       <c r="K70" t="s">
-        <v>622</v>
+        <v>419</v>
       </c>
     </row>
     <row r="71" spans="1:11">
-      <c r="A71" t="s">
-        <v>81</v>
+      <c r="A71">
+        <v>1.628416830455878E+18</v>
       </c>
       <c r="B71" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>288</v>
+        <v>85</v>
       </c>
       <c r="D71" t="s">
-        <v>472</v>
+        <v>269</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -5245,21 +4636,21 @@
         <v>184921</v>
       </c>
       <c r="K71" t="s">
-        <v>623</v>
+        <v>420</v>
       </c>
     </row>
     <row r="72" spans="1:11">
-      <c r="A72" t="s">
-        <v>82</v>
+      <c r="A72">
+        <v>1.628416198659527E+18</v>
       </c>
       <c r="B72" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>289</v>
+        <v>86</v>
       </c>
       <c r="D72" t="s">
-        <v>472</v>
+        <v>269</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -5280,21 +4671,21 @@
         <v>184921</v>
       </c>
       <c r="K72" t="s">
-        <v>623</v>
+        <v>420</v>
       </c>
     </row>
     <row r="73" spans="1:11">
-      <c r="A73" t="s">
-        <v>83</v>
+      <c r="A73">
+        <v>1.628159921660256E+18</v>
       </c>
       <c r="B73" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>290</v>
+        <v>87</v>
       </c>
       <c r="D73" t="s">
-        <v>473</v>
+        <v>270</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -5315,21 +4706,21 @@
         <v>125092</v>
       </c>
       <c r="K73" t="s">
-        <v>624</v>
+        <v>421</v>
       </c>
     </row>
     <row r="74" spans="1:11">
-      <c r="A74" t="s">
-        <v>84</v>
+      <c r="A74">
+        <v>1.662051837590077E+18</v>
       </c>
       <c r="B74" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>291</v>
+        <v>88</v>
       </c>
       <c r="D74" t="s">
-        <v>474</v>
+        <v>271</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -5350,21 +4741,21 @@
         <v>16315</v>
       </c>
       <c r="K74" t="s">
-        <v>625</v>
+        <v>422</v>
       </c>
     </row>
     <row r="75" spans="1:11">
-      <c r="A75" t="s">
-        <v>85</v>
+      <c r="A75">
+        <v>1.65085318455298E+18</v>
       </c>
       <c r="B75" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>292</v>
+        <v>89</v>
       </c>
       <c r="D75" t="s">
-        <v>475</v>
+        <v>272</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -5385,21 +4776,21 @@
         <v>40100</v>
       </c>
       <c r="K75" t="s">
-        <v>626</v>
+        <v>423</v>
       </c>
     </row>
     <row r="76" spans="1:11">
-      <c r="A76" t="s">
-        <v>86</v>
+      <c r="A76">
+        <v>1.641175498410672E+18</v>
       </c>
       <c r="B76" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>293</v>
+        <v>90</v>
       </c>
       <c r="D76" t="s">
-        <v>476</v>
+        <v>273</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -5420,21 +4811,21 @@
         <v>304681</v>
       </c>
       <c r="K76" t="s">
-        <v>627</v>
+        <v>424</v>
       </c>
     </row>
     <row r="77" spans="1:11">
-      <c r="A77" t="s">
-        <v>87</v>
+      <c r="A77">
+        <v>1.62850980415393E+18</v>
       </c>
       <c r="B77" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>294</v>
+        <v>91</v>
       </c>
       <c r="D77" t="s">
-        <v>471</v>
+        <v>268</v>
       </c>
       <c r="E77">
         <v>3195</v>
@@ -5455,21 +4846,21 @@
         <v>353004</v>
       </c>
       <c r="K77" t="s">
-        <v>622</v>
+        <v>419</v>
       </c>
     </row>
     <row r="78" spans="1:11">
-      <c r="A78" t="s">
-        <v>88</v>
+      <c r="A78">
+        <v>1.628469143472144E+18</v>
       </c>
       <c r="B78" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>295</v>
+        <v>92</v>
       </c>
       <c r="D78" t="s">
-        <v>471</v>
+        <v>268</v>
       </c>
       <c r="E78">
         <v>3195</v>
@@ -5490,21 +4881,21 @@
         <v>353004</v>
       </c>
       <c r="K78" t="s">
-        <v>622</v>
+        <v>419</v>
       </c>
     </row>
     <row r="79" spans="1:11">
-      <c r="A79" t="s">
-        <v>89</v>
+      <c r="A79">
+        <v>1.62815637377409E+18</v>
       </c>
       <c r="B79" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>296</v>
+        <v>93</v>
       </c>
       <c r="D79" t="s">
-        <v>473</v>
+        <v>270</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -5525,21 +4916,21 @@
         <v>125092</v>
       </c>
       <c r="K79" t="s">
-        <v>624</v>
+        <v>421</v>
       </c>
     </row>
     <row r="80" spans="1:11">
-      <c r="A80" t="s">
-        <v>90</v>
+      <c r="A80">
+        <v>1.627968217946759E+18</v>
       </c>
       <c r="B80" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>297</v>
+        <v>94</v>
       </c>
       <c r="D80" t="s">
-        <v>477</v>
+        <v>274</v>
       </c>
       <c r="E80">
         <v>5511</v>
@@ -5560,27 +4951,27 @@
         <v>720129</v>
       </c>
       <c r="K80" t="s">
-        <v>628</v>
+        <v>425</v>
       </c>
     </row>
     <row r="81" spans="1:11">
-      <c r="A81" t="s">
-        <v>91</v>
+      <c r="A81">
+        <v>1.627951140041097E+18</v>
       </c>
       <c r="B81" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>298</v>
+        <v>95</v>
       </c>
       <c r="D81" t="s">
-        <v>478</v>
+        <v>275</v>
       </c>
       <c r="E81">
-        <v>0</v>
+        <v>5511</v>
       </c>
       <c r="F81">
-        <v>0</v>
+        <v>1017</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -5592,24 +4983,24 @@
         <v>0</v>
       </c>
       <c r="J81">
-        <v>129</v>
+        <v>720129</v>
       </c>
       <c r="K81" t="s">
-        <v>629</v>
+        <v>426</v>
       </c>
     </row>
     <row r="82" spans="1:11">
-      <c r="A82" t="s">
-        <v>92</v>
+      <c r="A82">
+        <v>1.627951136610087E+18</v>
       </c>
       <c r="B82" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>299</v>
+        <v>96</v>
       </c>
       <c r="D82" t="s">
-        <v>477</v>
+        <v>274</v>
       </c>
       <c r="E82">
         <v>5511</v>
@@ -5630,21 +5021,21 @@
         <v>720129</v>
       </c>
       <c r="K82" t="s">
-        <v>628</v>
+        <v>425</v>
       </c>
     </row>
     <row r="83" spans="1:11">
-      <c r="A83" t="s">
-        <v>93</v>
+      <c r="A83">
+        <v>1.627951132671607E+18</v>
       </c>
       <c r="B83" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>300</v>
+        <v>97</v>
       </c>
       <c r="D83" t="s">
-        <v>477</v>
+        <v>274</v>
       </c>
       <c r="E83">
         <v>5511</v>
@@ -5665,21 +5056,21 @@
         <v>720129</v>
       </c>
       <c r="K83" t="s">
-        <v>628</v>
+        <v>425</v>
       </c>
     </row>
     <row r="84" spans="1:11">
-      <c r="A84" t="s">
-        <v>94</v>
+      <c r="A84">
+        <v>1.627942731166151E+18</v>
       </c>
       <c r="B84" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>301</v>
+        <v>98</v>
       </c>
       <c r="D84" t="s">
-        <v>477</v>
+        <v>274</v>
       </c>
       <c r="E84">
         <v>5511</v>
@@ -5700,21 +5091,21 @@
         <v>720129</v>
       </c>
       <c r="K84" t="s">
-        <v>628</v>
+        <v>425</v>
       </c>
     </row>
     <row r="85" spans="1:11">
-      <c r="A85" t="s">
-        <v>95</v>
+      <c r="A85">
+        <v>1.627942727752069E+18</v>
       </c>
       <c r="B85" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>302</v>
+        <v>99</v>
       </c>
       <c r="D85" t="s">
-        <v>477</v>
+        <v>274</v>
       </c>
       <c r="E85">
         <v>5511</v>
@@ -5735,21 +5126,21 @@
         <v>720129</v>
       </c>
       <c r="K85" t="s">
-        <v>628</v>
+        <v>425</v>
       </c>
     </row>
     <row r="86" spans="1:11">
-      <c r="A86" t="s">
-        <v>96</v>
+      <c r="A86">
+        <v>1.627942720940433E+18</v>
       </c>
       <c r="B86" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>303</v>
+        <v>100</v>
       </c>
       <c r="D86" t="s">
-        <v>477</v>
+        <v>274</v>
       </c>
       <c r="E86">
         <v>5511</v>
@@ -5770,21 +5161,21 @@
         <v>720129</v>
       </c>
       <c r="K86" t="s">
-        <v>628</v>
+        <v>425</v>
       </c>
     </row>
     <row r="87" spans="1:11">
-      <c r="A87" t="s">
-        <v>97</v>
+      <c r="A87">
+        <v>1.627942717320843E+18</v>
       </c>
       <c r="B87" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>304</v>
+        <v>101</v>
       </c>
       <c r="D87" t="s">
-        <v>477</v>
+        <v>274</v>
       </c>
       <c r="E87">
         <v>5511</v>
@@ -5805,21 +5196,21 @@
         <v>720129</v>
       </c>
       <c r="K87" t="s">
-        <v>628</v>
+        <v>425</v>
       </c>
     </row>
     <row r="88" spans="1:11">
-      <c r="A88" t="s">
-        <v>98</v>
+      <c r="A88">
+        <v>1.627281039818207E+18</v>
       </c>
       <c r="B88" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>305</v>
+        <v>102</v>
       </c>
       <c r="D88" t="s">
-        <v>479</v>
+        <v>276</v>
       </c>
       <c r="E88">
         <v>7254</v>
@@ -5840,21 +5231,21 @@
         <v>444575</v>
       </c>
       <c r="K88" t="s">
-        <v>630</v>
+        <v>427</v>
       </c>
     </row>
     <row r="89" spans="1:11">
-      <c r="A89" t="s">
-        <v>99</v>
+      <c r="A89">
+        <v>1.62047512857557E+18</v>
       </c>
       <c r="B89" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>306</v>
+        <v>103</v>
       </c>
       <c r="D89" t="s">
-        <v>480</v>
+        <v>277</v>
       </c>
       <c r="E89">
         <v>3091</v>
@@ -5875,21 +5266,21 @@
         <v>121562</v>
       </c>
       <c r="K89" t="s">
-        <v>631</v>
+        <v>428</v>
       </c>
     </row>
     <row r="90" spans="1:11">
-      <c r="A90" t="s">
-        <v>100</v>
+      <c r="A90">
+        <v>1.620466505115894E+18</v>
       </c>
       <c r="B90" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>307</v>
+        <v>104</v>
       </c>
       <c r="D90" t="s">
-        <v>480</v>
+        <v>277</v>
       </c>
       <c r="E90">
         <v>3091</v>
@@ -5910,21 +5301,21 @@
         <v>121562</v>
       </c>
       <c r="K90" t="s">
-        <v>631</v>
+        <v>428</v>
       </c>
     </row>
     <row r="91" spans="1:11">
-      <c r="A91" t="s">
-        <v>101</v>
+      <c r="A91">
+        <v>1.620386661296382E+18</v>
       </c>
       <c r="B91" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>308</v>
+        <v>105</v>
       </c>
       <c r="D91" t="s">
-        <v>481</v>
+        <v>278</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -5945,30 +5336,30 @@
         <v>13290</v>
       </c>
       <c r="K91" t="s">
-        <v>632</v>
+        <v>429</v>
       </c>
     </row>
     <row r="92" spans="1:11">
-      <c r="A92" t="s">
-        <v>102</v>
+      <c r="A92">
+        <v>1.620377121280659E+18</v>
       </c>
       <c r="B92" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>309</v>
+        <v>106</v>
       </c>
       <c r="D92" t="s">
-        <v>482</v>
+        <v>279</v>
       </c>
       <c r="E92">
-        <v>0</v>
+        <v>8574</v>
       </c>
       <c r="F92">
-        <v>0</v>
+        <v>1755</v>
       </c>
       <c r="G92">
-        <v>0</v>
+        <v>277</v>
       </c>
       <c r="H92">
         <v>0</v>
@@ -5977,30 +5368,30 @@
         <v>0</v>
       </c>
       <c r="J92">
-        <v>489291</v>
+        <v>489292</v>
       </c>
       <c r="K92" t="s">
-        <v>633</v>
+        <v>430</v>
       </c>
     </row>
     <row r="93" spans="1:11">
-      <c r="A93" t="s">
-        <v>103</v>
+      <c r="A93">
+        <v>1.620034619918922E+18</v>
       </c>
       <c r="B93" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>310</v>
+        <v>107</v>
       </c>
       <c r="D93" t="s">
-        <v>483</v>
+        <v>280</v>
       </c>
       <c r="E93">
-        <v>0</v>
+        <v>4153</v>
       </c>
       <c r="F93">
-        <v>0</v>
+        <v>1078</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -6015,24 +5406,24 @@
         <v>193039</v>
       </c>
       <c r="K93" t="s">
-        <v>634</v>
+        <v>431</v>
       </c>
     </row>
     <row r="94" spans="1:11">
-      <c r="A94" t="s">
-        <v>104</v>
+      <c r="A94">
+        <v>1.619354933362569E+18</v>
       </c>
       <c r="B94" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>311</v>
+        <v>108</v>
       </c>
       <c r="D94" t="s">
-        <v>484</v>
+        <v>281</v>
       </c>
       <c r="E94">
-        <v>0</v>
+        <v>2739</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -6050,21 +5441,21 @@
         <v>111207</v>
       </c>
       <c r="K94" t="s">
-        <v>635</v>
+        <v>432</v>
       </c>
     </row>
     <row r="95" spans="1:11">
-      <c r="A95" t="s">
-        <v>105</v>
+      <c r="A95">
+        <v>1.619000891243373E+18</v>
       </c>
       <c r="B95" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>312</v>
+        <v>109</v>
       </c>
       <c r="D95" t="s">
-        <v>485</v>
+        <v>282</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -6085,30 +5476,30 @@
         <v>327005</v>
       </c>
       <c r="K95" t="s">
-        <v>636</v>
+        <v>433</v>
       </c>
     </row>
     <row r="96" spans="1:11">
-      <c r="A96" t="s">
-        <v>106</v>
+      <c r="A96">
+        <v>1.618655300382511E+18</v>
       </c>
       <c r="B96" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>313</v>
+        <v>110</v>
       </c>
       <c r="D96" t="s">
-        <v>486</v>
+        <v>283</v>
       </c>
       <c r="E96">
-        <v>0</v>
+        <v>7259</v>
       </c>
       <c r="F96">
-        <v>0</v>
+        <v>1416</v>
       </c>
       <c r="G96">
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="H96">
         <v>0</v>
@@ -6120,21 +5511,21 @@
         <v>368970</v>
       </c>
       <c r="K96" t="s">
-        <v>637</v>
+        <v>434</v>
       </c>
     </row>
     <row r="97" spans="1:11">
-      <c r="A97" t="s">
-        <v>107</v>
+      <c r="A97">
+        <v>1.618258019317604E+18</v>
       </c>
       <c r="B97" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>314</v>
+        <v>111</v>
       </c>
       <c r="D97" t="s">
-        <v>487</v>
+        <v>284</v>
       </c>
       <c r="E97">
         <v>3854</v>
@@ -6155,21 +5546,21 @@
         <v>162362</v>
       </c>
       <c r="K97" t="s">
-        <v>638</v>
+        <v>435</v>
       </c>
     </row>
     <row r="98" spans="1:11">
-      <c r="A98" t="s">
-        <v>108</v>
+      <c r="A98">
+        <v>1.618256715186831E+18</v>
       </c>
       <c r="B98" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>315</v>
+        <v>112</v>
       </c>
       <c r="D98" t="s">
-        <v>487</v>
+        <v>284</v>
       </c>
       <c r="E98">
         <v>3854</v>
@@ -6190,21 +5581,21 @@
         <v>162362</v>
       </c>
       <c r="K98" t="s">
-        <v>638</v>
+        <v>435</v>
       </c>
     </row>
     <row r="99" spans="1:11">
-      <c r="A99" t="s">
-        <v>109</v>
+      <c r="A99">
+        <v>1.618239180903174E+18</v>
       </c>
       <c r="B99" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>316</v>
+        <v>113</v>
       </c>
       <c r="D99" t="s">
-        <v>488</v>
+        <v>285</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -6225,21 +5616,21 @@
         <v>199730</v>
       </c>
       <c r="K99" t="s">
-        <v>639</v>
+        <v>436</v>
       </c>
     </row>
     <row r="100" spans="1:11">
-      <c r="A100" t="s">
-        <v>110</v>
+      <c r="A100">
+        <v>1.686113646470902E+18</v>
       </c>
       <c r="B100" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>317</v>
+        <v>114</v>
       </c>
       <c r="D100" t="s">
-        <v>489</v>
+        <v>286</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -6260,21 +5651,21 @@
         <v>71996</v>
       </c>
       <c r="K100" t="s">
-        <v>640</v>
+        <v>437</v>
       </c>
     </row>
     <row r="101" spans="1:11">
-      <c r="A101" t="s">
-        <v>111</v>
+      <c r="A101">
+        <v>1.686081505393553E+18</v>
       </c>
       <c r="B101" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>318</v>
+        <v>115</v>
       </c>
       <c r="D101" t="s">
-        <v>490</v>
+        <v>287</v>
       </c>
       <c r="E101">
         <v>3223</v>
@@ -6295,21 +5686,21 @@
         <v>335821</v>
       </c>
       <c r="K101" t="s">
-        <v>641</v>
+        <v>438</v>
       </c>
     </row>
     <row r="102" spans="1:11">
-      <c r="A102" t="s">
-        <v>112</v>
+      <c r="A102">
+        <v>1.674877960300511E+18</v>
       </c>
       <c r="B102" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>319</v>
+        <v>116</v>
       </c>
       <c r="D102" t="s">
-        <v>491</v>
+        <v>288</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6330,21 +5721,21 @@
         <v>56409</v>
       </c>
       <c r="K102" t="s">
-        <v>642</v>
+        <v>439</v>
       </c>
     </row>
     <row r="103" spans="1:11">
-      <c r="A103" t="s">
-        <v>113</v>
+      <c r="A103">
+        <v>1.674876125061816E+18</v>
       </c>
       <c r="B103" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>320</v>
+        <v>117</v>
       </c>
       <c r="D103" t="s">
-        <v>492</v>
+        <v>289</v>
       </c>
       <c r="E103">
         <v>734</v>
@@ -6365,21 +5756,21 @@
         <v>22044</v>
       </c>
       <c r="K103" t="s">
-        <v>643</v>
+        <v>440</v>
       </c>
     </row>
     <row r="104" spans="1:11">
-      <c r="A104" t="s">
-        <v>114</v>
+      <c r="A104">
+        <v>1.674869498929635E+18</v>
       </c>
       <c r="B104" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>321</v>
+        <v>118</v>
       </c>
       <c r="D104" t="s">
-        <v>493</v>
+        <v>290</v>
       </c>
       <c r="E104">
         <v>1988</v>
@@ -6400,21 +5791,21 @@
         <v>111454</v>
       </c>
       <c r="K104" t="s">
-        <v>644</v>
+        <v>441</v>
       </c>
     </row>
     <row r="105" spans="1:11">
-      <c r="A105" t="s">
-        <v>115</v>
+      <c r="A105">
+        <v>1.6748566759902E+18</v>
       </c>
       <c r="B105" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>322</v>
+        <v>119</v>
       </c>
       <c r="D105" t="s">
-        <v>494</v>
+        <v>291</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -6435,21 +5826,21 @@
         <v>35904</v>
       </c>
       <c r="K105" t="s">
-        <v>645</v>
+        <v>442</v>
       </c>
     </row>
     <row r="106" spans="1:11">
-      <c r="A106" t="s">
-        <v>116</v>
+      <c r="A106">
+        <v>1.67485453228562E+18</v>
       </c>
       <c r="B106" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>323</v>
+        <v>120</v>
       </c>
       <c r="D106" t="s">
-        <v>495</v>
+        <v>292</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -6470,21 +5861,21 @@
         <v>274719</v>
       </c>
       <c r="K106" t="s">
-        <v>646</v>
+        <v>443</v>
       </c>
     </row>
     <row r="107" spans="1:11">
-      <c r="A107" t="s">
-        <v>117</v>
+      <c r="A107">
+        <v>1.664013082002092E+18</v>
       </c>
       <c r="B107" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>324</v>
+        <v>121</v>
       </c>
       <c r="D107" t="s">
-        <v>496</v>
+        <v>293</v>
       </c>
       <c r="E107">
         <v>838</v>
@@ -6505,21 +5896,21 @@
         <v>28462</v>
       </c>
       <c r="K107" t="s">
-        <v>647</v>
+        <v>444</v>
       </c>
     </row>
     <row r="108" spans="1:11">
-      <c r="A108" t="s">
-        <v>118</v>
+      <c r="A108">
+        <v>1.663979405817856E+18</v>
       </c>
       <c r="B108" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>325</v>
+        <v>122</v>
       </c>
       <c r="D108" t="s">
-        <v>497</v>
+        <v>294</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -6540,21 +5931,21 @@
         <v>319799</v>
       </c>
       <c r="K108" t="s">
-        <v>648</v>
+        <v>445</v>
       </c>
     </row>
     <row r="109" spans="1:11">
-      <c r="A109" t="s">
-        <v>119</v>
+      <c r="A109">
+        <v>1.663974406429843E+18</v>
       </c>
       <c r="B109" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>326</v>
+        <v>123</v>
       </c>
       <c r="D109" t="s">
-        <v>497</v>
+        <v>294</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -6575,21 +5966,21 @@
         <v>319799</v>
       </c>
       <c r="K109" t="s">
-        <v>648</v>
+        <v>445</v>
       </c>
     </row>
     <row r="110" spans="1:11">
-      <c r="A110" t="s">
-        <v>120</v>
+      <c r="A110">
+        <v>1.663973546870096E+18</v>
       </c>
       <c r="B110" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>327</v>
+        <v>124</v>
       </c>
       <c r="D110" t="s">
-        <v>497</v>
+        <v>294</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -6610,21 +6001,21 @@
         <v>319799</v>
       </c>
       <c r="K110" t="s">
-        <v>648</v>
+        <v>445</v>
       </c>
     </row>
     <row r="111" spans="1:11">
-      <c r="A111" t="s">
-        <v>121</v>
+      <c r="A111">
+        <v>1.663872465410335E+18</v>
       </c>
       <c r="B111" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>328</v>
+        <v>125</v>
       </c>
       <c r="D111" t="s">
-        <v>498</v>
+        <v>295</v>
       </c>
       <c r="E111">
         <v>1159</v>
@@ -6645,21 +6036,21 @@
         <v>33036</v>
       </c>
       <c r="K111" t="s">
-        <v>649</v>
+        <v>446</v>
       </c>
     </row>
     <row r="112" spans="1:11">
-      <c r="A112" t="s">
-        <v>122</v>
+      <c r="A112">
+        <v>1.663830983601267E+18</v>
       </c>
       <c r="B112" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>329</v>
+        <v>126</v>
       </c>
       <c r="D112" t="s">
-        <v>499</v>
+        <v>296</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -6680,21 +6071,21 @@
         <v>46420</v>
       </c>
       <c r="K112" t="s">
-        <v>650</v>
+        <v>447</v>
       </c>
     </row>
     <row r="113" spans="1:11">
-      <c r="A113" t="s">
-        <v>123</v>
+      <c r="A113">
+        <v>1.663822494107591E+18</v>
       </c>
       <c r="B113" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>330</v>
+        <v>127</v>
       </c>
       <c r="D113" t="s">
-        <v>500</v>
+        <v>297</v>
       </c>
       <c r="E113">
         <v>547</v>
@@ -6715,21 +6106,21 @@
         <v>19626</v>
       </c>
       <c r="K113" t="s">
-        <v>651</v>
+        <v>448</v>
       </c>
     </row>
     <row r="114" spans="1:11">
-      <c r="A114" t="s">
-        <v>124</v>
+      <c r="A114">
+        <v>1.66381894850306E+18</v>
       </c>
       <c r="B114" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>331</v>
+        <v>128</v>
       </c>
       <c r="D114" t="s">
-        <v>501</v>
+        <v>298</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -6750,21 +6141,21 @@
         <v>71104</v>
       </c>
       <c r="K114" t="s">
-        <v>652</v>
+        <v>449</v>
       </c>
     </row>
     <row r="115" spans="1:11">
-      <c r="A115" t="s">
-        <v>125</v>
+      <c r="A115">
+        <v>1.663801008604996E+18</v>
       </c>
       <c r="B115" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>332</v>
+        <v>129</v>
       </c>
       <c r="D115" t="s">
-        <v>502</v>
+        <v>299</v>
       </c>
       <c r="E115">
         <v>686</v>
@@ -6785,21 +6176,21 @@
         <v>37548</v>
       </c>
       <c r="K115" t="s">
-        <v>653</v>
+        <v>450</v>
       </c>
     </row>
     <row r="116" spans="1:11">
-      <c r="A116" t="s">
-        <v>126</v>
+      <c r="A116">
+        <v>1.663628568440582E+18</v>
       </c>
       <c r="B116" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>333</v>
+        <v>130</v>
       </c>
       <c r="D116" t="s">
-        <v>503</v>
+        <v>300</v>
       </c>
       <c r="E116">
         <v>1043</v>
@@ -6820,21 +6211,21 @@
         <v>155239</v>
       </c>
       <c r="K116" t="s">
-        <v>654</v>
+        <v>451</v>
       </c>
     </row>
     <row r="117" spans="1:11">
-      <c r="A117" t="s">
-        <v>127</v>
+      <c r="A117">
+        <v>1.663626533565497E+18</v>
       </c>
       <c r="B117" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>334</v>
+        <v>131</v>
       </c>
       <c r="D117" t="s">
-        <v>504</v>
+        <v>301</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -6855,21 +6246,21 @@
         <v>47822</v>
       </c>
       <c r="K117" t="s">
-        <v>655</v>
+        <v>452</v>
       </c>
     </row>
     <row r="118" spans="1:11">
-      <c r="A118" t="s">
-        <v>128</v>
+      <c r="A118">
+        <v>1.652779124778316E+18</v>
       </c>
       <c r="B118" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>335</v>
+        <v>132</v>
       </c>
       <c r="D118" t="s">
-        <v>505</v>
+        <v>302</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -6890,21 +6281,21 @@
         <v>249877</v>
       </c>
       <c r="K118" t="s">
-        <v>656</v>
+        <v>453</v>
       </c>
     </row>
     <row r="119" spans="1:11">
-      <c r="A119" t="s">
-        <v>129</v>
+      <c r="A119">
+        <v>1.652761869009011E+18</v>
       </c>
       <c r="B119" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>336</v>
+        <v>133</v>
       </c>
       <c r="D119" t="s">
-        <v>506</v>
+        <v>303</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -6925,21 +6316,21 @@
         <v>77825</v>
       </c>
       <c r="K119" t="s">
-        <v>657</v>
+        <v>454</v>
       </c>
     </row>
     <row r="120" spans="1:11">
-      <c r="A120" t="s">
-        <v>130</v>
+      <c r="A120">
+        <v>1.652759441123553E+18</v>
       </c>
       <c r="B120" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>337</v>
+        <v>134</v>
       </c>
       <c r="D120" t="s">
-        <v>507</v>
+        <v>304</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -6960,21 +6351,21 @@
         <v>45356</v>
       </c>
       <c r="K120" t="s">
-        <v>658</v>
+        <v>455</v>
       </c>
     </row>
     <row r="121" spans="1:11">
-      <c r="A121" t="s">
-        <v>131</v>
+      <c r="A121">
+        <v>1.652752531469005E+18</v>
       </c>
       <c r="B121" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>338</v>
+        <v>135</v>
       </c>
       <c r="D121" t="s">
-        <v>508</v>
+        <v>305</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -6995,21 +6386,21 @@
         <v>79762</v>
       </c>
       <c r="K121" t="s">
-        <v>659</v>
+        <v>456</v>
       </c>
     </row>
     <row r="122" spans="1:11">
-      <c r="A122" t="s">
-        <v>132</v>
+      <c r="A122">
+        <v>1.652668333668327E+18</v>
       </c>
       <c r="B122" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>339</v>
+        <v>136</v>
       </c>
       <c r="D122" t="s">
-        <v>509</v>
+        <v>306</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -7030,21 +6421,21 @@
         <v>49196</v>
       </c>
       <c r="K122" t="s">
-        <v>660</v>
+        <v>457</v>
       </c>
     </row>
     <row r="123" spans="1:11">
-      <c r="A123" t="s">
-        <v>133</v>
+      <c r="A123">
+        <v>1.652592217830175E+18</v>
       </c>
       <c r="B123" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>340</v>
+        <v>137</v>
       </c>
       <c r="D123" t="s">
-        <v>510</v>
+        <v>307</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -7065,21 +6456,21 @@
         <v>46759</v>
       </c>
       <c r="K123" t="s">
-        <v>661</v>
+        <v>458</v>
       </c>
     </row>
     <row r="124" spans="1:11">
-      <c r="A124" t="s">
-        <v>134</v>
+      <c r="A124">
+        <v>1.641321315909923E+18</v>
       </c>
       <c r="B124" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>341</v>
+        <v>138</v>
       </c>
       <c r="D124" t="s">
-        <v>511</v>
+        <v>308</v>
       </c>
       <c r="E124">
         <v>398</v>
@@ -7100,21 +6491,21 @@
         <v>38476</v>
       </c>
       <c r="K124" t="s">
-        <v>662</v>
+        <v>459</v>
       </c>
     </row>
     <row r="125" spans="1:11">
-      <c r="A125" t="s">
-        <v>135</v>
+      <c r="A125">
+        <v>1.641315964141683E+18</v>
       </c>
       <c r="B125" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>342</v>
+        <v>139</v>
       </c>
       <c r="D125" t="s">
-        <v>512</v>
+        <v>309</v>
       </c>
       <c r="E125">
         <v>494</v>
@@ -7135,21 +6526,21 @@
         <v>47362</v>
       </c>
       <c r="K125" t="s">
-        <v>663</v>
+        <v>460</v>
       </c>
     </row>
     <row r="126" spans="1:11">
-      <c r="A126" t="s">
-        <v>136</v>
+      <c r="A126">
+        <v>1.641174459674403E+18</v>
       </c>
       <c r="B126" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>343</v>
+        <v>140</v>
       </c>
       <c r="D126" t="s">
-        <v>513</v>
+        <v>310</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -7170,21 +6561,21 @@
         <v>33017</v>
       </c>
       <c r="K126" t="s">
-        <v>664</v>
+        <v>461</v>
       </c>
     </row>
     <row r="127" spans="1:11">
-      <c r="A127" t="s">
-        <v>137</v>
+      <c r="A127">
+        <v>1.641155860255654E+18</v>
       </c>
       <c r="B127" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>344</v>
+        <v>141</v>
       </c>
       <c r="D127" t="s">
-        <v>514</v>
+        <v>311</v>
       </c>
       <c r="E127">
         <v>4580</v>
@@ -7205,21 +6596,21 @@
         <v>321825</v>
       </c>
       <c r="K127" t="s">
-        <v>665</v>
+        <v>462</v>
       </c>
     </row>
     <row r="128" spans="1:11">
-      <c r="A128" t="s">
-        <v>138</v>
+      <c r="A128">
+        <v>1.641047468832969E+18</v>
       </c>
       <c r="B128" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>345</v>
+        <v>142</v>
       </c>
       <c r="D128" t="s">
-        <v>515</v>
+        <v>312</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -7240,21 +6631,21 @@
         <v>186069</v>
       </c>
       <c r="K128" t="s">
-        <v>666</v>
+        <v>463</v>
       </c>
     </row>
     <row r="129" spans="1:11">
-      <c r="A129" t="s">
-        <v>139</v>
+      <c r="A129">
+        <v>1.620540014445859E+18</v>
       </c>
       <c r="B129" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>346</v>
+        <v>143</v>
       </c>
       <c r="D129" t="s">
-        <v>516</v>
+        <v>313</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -7275,21 +6666,21 @@
         <v>32959</v>
       </c>
       <c r="K129" t="s">
-        <v>667</v>
+        <v>464</v>
       </c>
     </row>
     <row r="130" spans="1:11">
-      <c r="A130" t="s">
-        <v>140</v>
+      <c r="A130">
+        <v>1.620530919324123E+18</v>
       </c>
       <c r="B130" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>347</v>
+        <v>144</v>
       </c>
       <c r="D130" t="s">
-        <v>517</v>
+        <v>314</v>
       </c>
       <c r="E130">
         <v>792</v>
@@ -7310,21 +6701,21 @@
         <v>26755</v>
       </c>
       <c r="K130" t="s">
-        <v>668</v>
+        <v>465</v>
       </c>
     </row>
     <row r="131" spans="1:11">
-      <c r="A131" t="s">
-        <v>141</v>
+      <c r="A131">
+        <v>1.620526658288755E+18</v>
       </c>
       <c r="B131" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>348</v>
+        <v>145</v>
       </c>
       <c r="D131" t="s">
-        <v>518</v>
+        <v>315</v>
       </c>
       <c r="E131">
         <v>619</v>
@@ -7345,21 +6736,21 @@
         <v>29157</v>
       </c>
       <c r="K131" t="s">
-        <v>669</v>
+        <v>466</v>
       </c>
     </row>
     <row r="132" spans="1:11">
-      <c r="A132" t="s">
-        <v>142</v>
+      <c r="A132">
+        <v>1.620496527683899E+18</v>
       </c>
       <c r="B132" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>349</v>
+        <v>146</v>
       </c>
       <c r="D132" t="s">
-        <v>519</v>
+        <v>316</v>
       </c>
       <c r="E132">
         <v>732</v>
@@ -7380,21 +6771,21 @@
         <v>30499</v>
       </c>
       <c r="K132" t="s">
-        <v>670</v>
+        <v>467</v>
       </c>
     </row>
     <row r="133" spans="1:11">
-      <c r="A133" t="s">
-        <v>143</v>
+      <c r="A133">
+        <v>1.620469226896249E+18</v>
       </c>
       <c r="B133" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>350</v>
+        <v>147</v>
       </c>
       <c r="D133" t="s">
-        <v>520</v>
+        <v>317</v>
       </c>
       <c r="E133">
         <v>204</v>
@@ -7415,21 +6806,21 @@
         <v>21617</v>
       </c>
       <c r="K133" t="s">
-        <v>671</v>
+        <v>468</v>
       </c>
     </row>
     <row r="134" spans="1:11">
-      <c r="A134" t="s">
-        <v>144</v>
+      <c r="A134">
+        <v>1.620401683191992E+18</v>
       </c>
       <c r="B134" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>351</v>
+        <v>148</v>
       </c>
       <c r="D134" t="s">
-        <v>521</v>
+        <v>318</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -7450,21 +6841,21 @@
         <v>284828</v>
       </c>
       <c r="K134" t="s">
-        <v>672</v>
+        <v>469</v>
       </c>
     </row>
     <row r="135" spans="1:11">
-      <c r="A135" t="s">
-        <v>145</v>
+      <c r="A135">
+        <v>1.620368805393465E+18</v>
       </c>
       <c r="B135" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>352</v>
+        <v>149</v>
       </c>
       <c r="D135" t="s">
-        <v>522</v>
+        <v>319</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -7485,21 +6876,21 @@
         <v>102668</v>
       </c>
       <c r="K135" t="s">
-        <v>673</v>
+        <v>470</v>
       </c>
     </row>
     <row r="136" spans="1:11">
-      <c r="A136" t="s">
-        <v>146</v>
+      <c r="A136">
+        <v>1.620328531157991E+18</v>
       </c>
       <c r="B136" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>353</v>
+        <v>150</v>
       </c>
       <c r="D136" t="s">
-        <v>523</v>
+        <v>320</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -7520,21 +6911,21 @@
         <v>35626</v>
       </c>
       <c r="K136" t="s">
-        <v>674</v>
+        <v>471</v>
       </c>
     </row>
     <row r="137" spans="1:11">
-      <c r="A137" t="s">
-        <v>147</v>
+      <c r="A137">
+        <v>1.641155845353292E+18</v>
       </c>
       <c r="B137" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>354</v>
+        <v>151</v>
       </c>
       <c r="D137" t="s">
-        <v>514</v>
+        <v>311</v>
       </c>
       <c r="E137">
         <v>4580</v>
@@ -7555,21 +6946,21 @@
         <v>321825</v>
       </c>
       <c r="K137" t="s">
-        <v>665</v>
+        <v>462</v>
       </c>
     </row>
     <row r="138" spans="1:11">
-      <c r="A138" t="s">
-        <v>148</v>
+      <c r="A138">
+        <v>1.641155820632044E+18</v>
       </c>
       <c r="B138" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>355</v>
+        <v>152</v>
       </c>
       <c r="D138" t="s">
-        <v>514</v>
+        <v>311</v>
       </c>
       <c r="E138">
         <v>4580</v>
@@ -7590,21 +6981,21 @@
         <v>321825</v>
       </c>
       <c r="K138" t="s">
-        <v>665</v>
+        <v>462</v>
       </c>
     </row>
     <row r="139" spans="1:11">
-      <c r="A139" t="s">
-        <v>149</v>
+      <c r="A139">
+        <v>1.641097671443087E+18</v>
       </c>
       <c r="B139" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>356</v>
+        <v>153</v>
       </c>
       <c r="D139" t="s">
-        <v>524</v>
+        <v>321</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -7625,21 +7016,21 @@
         <v>48149</v>
       </c>
       <c r="K139" t="s">
-        <v>675</v>
+        <v>472</v>
       </c>
     </row>
     <row r="140" spans="1:11">
-      <c r="A140" t="s">
-        <v>150</v>
+      <c r="A140">
+        <v>1.64108767642096E+18</v>
       </c>
       <c r="B140" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>357</v>
+        <v>154</v>
       </c>
       <c r="D140" t="s">
-        <v>525</v>
+        <v>322</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -7660,21 +7051,21 @@
         <v>108944</v>
       </c>
       <c r="K140" t="s">
-        <v>676</v>
+        <v>473</v>
       </c>
     </row>
     <row r="141" spans="1:11">
-      <c r="A141" t="s">
-        <v>151</v>
+      <c r="A141">
+        <v>1.620368773386756E+18</v>
       </c>
       <c r="B141" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>358</v>
+        <v>155</v>
       </c>
       <c r="D141" t="s">
-        <v>522</v>
+        <v>319</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -7695,21 +7086,21 @@
         <v>102668</v>
       </c>
       <c r="K141" t="s">
-        <v>673</v>
+        <v>470</v>
       </c>
     </row>
     <row r="142" spans="1:11">
-      <c r="A142" t="s">
-        <v>152</v>
+      <c r="A142">
+        <v>1.620368770975007E+18</v>
       </c>
       <c r="B142" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>359</v>
+        <v>156</v>
       </c>
       <c r="D142" t="s">
-        <v>522</v>
+        <v>319</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -7730,21 +7121,21 @@
         <v>102668</v>
       </c>
       <c r="K142" t="s">
-        <v>673</v>
+        <v>470</v>
       </c>
     </row>
     <row r="143" spans="1:11">
-      <c r="A143" t="s">
-        <v>153</v>
+      <c r="A143">
+        <v>1.620340976228389E+18</v>
       </c>
       <c r="B143" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>360</v>
+        <v>157</v>
       </c>
       <c r="D143" t="s">
-        <v>526</v>
+        <v>323</v>
       </c>
       <c r="E143">
         <v>0</v>
@@ -7765,21 +7156,21 @@
         <v>220850</v>
       </c>
       <c r="K143" t="s">
-        <v>677</v>
+        <v>474</v>
       </c>
     </row>
     <row r="144" spans="1:11">
-      <c r="A144" t="s">
-        <v>154</v>
+      <c r="A144">
+        <v>1.663996285093835E+18</v>
       </c>
       <c r="B144" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>361</v>
+        <v>158</v>
       </c>
       <c r="D144" t="s">
-        <v>527</v>
+        <v>324</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -7800,21 +7191,21 @@
         <v>86793</v>
       </c>
       <c r="K144" t="s">
-        <v>678</v>
+        <v>475</v>
       </c>
     </row>
     <row r="145" spans="1:11">
-      <c r="A145" t="s">
-        <v>155</v>
+      <c r="A145">
+        <v>1.663996251531014E+18</v>
       </c>
       <c r="B145" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>362</v>
+        <v>159</v>
       </c>
       <c r="D145" t="s">
-        <v>527</v>
+        <v>324</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -7835,21 +7226,21 @@
         <v>86793</v>
       </c>
       <c r="K145" t="s">
-        <v>678</v>
+        <v>475</v>
       </c>
     </row>
     <row r="146" spans="1:11">
-      <c r="A146" t="s">
-        <v>156</v>
+      <c r="A146">
+        <v>1.66399624578909E+18</v>
       </c>
       <c r="B146" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>363</v>
+        <v>160</v>
       </c>
       <c r="D146" t="s">
-        <v>527</v>
+        <v>324</v>
       </c>
       <c r="E146">
         <v>0</v>
@@ -7870,21 +7261,21 @@
         <v>86793</v>
       </c>
       <c r="K146" t="s">
-        <v>678</v>
+        <v>475</v>
       </c>
     </row>
     <row r="147" spans="1:11">
-      <c r="A147" t="s">
-        <v>157</v>
+      <c r="A147">
+        <v>1.663980911627518E+18</v>
       </c>
       <c r="B147" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>364</v>
+        <v>161</v>
       </c>
       <c r="D147" t="s">
-        <v>497</v>
+        <v>294</v>
       </c>
       <c r="E147">
         <v>0</v>
@@ -7905,21 +7296,21 @@
         <v>319799</v>
       </c>
       <c r="K147" t="s">
-        <v>648</v>
+        <v>445</v>
       </c>
     </row>
     <row r="148" spans="1:11">
-      <c r="A148" t="s">
-        <v>158</v>
+      <c r="A148">
+        <v>1.663979994899464E+18</v>
       </c>
       <c r="B148" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>365</v>
+        <v>162</v>
       </c>
       <c r="D148" t="s">
-        <v>497</v>
+        <v>294</v>
       </c>
       <c r="E148">
         <v>0</v>
@@ -7940,21 +7331,21 @@
         <v>319799</v>
       </c>
       <c r="K148" t="s">
-        <v>648</v>
+        <v>445</v>
       </c>
     </row>
     <row r="149" spans="1:11">
-      <c r="A149" t="s">
-        <v>159</v>
+      <c r="A149">
+        <v>1.663976426515644E+18</v>
       </c>
       <c r="B149" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>366</v>
+        <v>163</v>
       </c>
       <c r="D149" t="s">
-        <v>497</v>
+        <v>294</v>
       </c>
       <c r="E149">
         <v>0</v>
@@ -7975,21 +7366,21 @@
         <v>319799</v>
       </c>
       <c r="K149" t="s">
-        <v>648</v>
+        <v>445</v>
       </c>
     </row>
     <row r="150" spans="1:11">
-      <c r="A150" t="s">
-        <v>160</v>
+      <c r="A150">
+        <v>1.663974891501105E+18</v>
       </c>
       <c r="B150" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>367</v>
+        <v>164</v>
       </c>
       <c r="D150" t="s">
-        <v>497</v>
+        <v>294</v>
       </c>
       <c r="E150">
         <v>0</v>
@@ -8010,21 +7401,21 @@
         <v>319799</v>
       </c>
       <c r="K150" t="s">
-        <v>648</v>
+        <v>445</v>
       </c>
     </row>
     <row r="151" spans="1:11">
-      <c r="A151" t="s">
-        <v>161</v>
+      <c r="A151">
+        <v>1.641155849115582E+18</v>
       </c>
       <c r="B151" t="s">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>368</v>
+        <v>165</v>
       </c>
       <c r="D151" t="s">
-        <v>514</v>
+        <v>311</v>
       </c>
       <c r="E151">
         <v>4580</v>
@@ -8045,21 +7436,21 @@
         <v>321825</v>
       </c>
       <c r="K151" t="s">
-        <v>665</v>
+        <v>462</v>
       </c>
     </row>
     <row r="152" spans="1:11">
-      <c r="A152" t="s">
-        <v>162</v>
+      <c r="A152">
+        <v>1.664054075162341E+18</v>
       </c>
       <c r="B152" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>369</v>
+        <v>166</v>
       </c>
       <c r="D152" t="s">
-        <v>528</v>
+        <v>325</v>
       </c>
       <c r="E152">
         <v>1170</v>
@@ -8080,21 +7471,21 @@
         <v>229579</v>
       </c>
       <c r="K152" t="s">
-        <v>679</v>
+        <v>476</v>
       </c>
     </row>
     <row r="153" spans="1:11">
-      <c r="A153" t="s">
-        <v>163</v>
+      <c r="A153">
+        <v>1.664050449861734E+18</v>
       </c>
       <c r="B153" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>370</v>
+        <v>167</v>
       </c>
       <c r="D153" t="s">
-        <v>529</v>
+        <v>326</v>
       </c>
       <c r="E153">
         <v>86</v>
@@ -8115,21 +7506,21 @@
         <v>6890</v>
       </c>
       <c r="K153" t="s">
-        <v>680</v>
+        <v>477</v>
       </c>
     </row>
     <row r="154" spans="1:11">
-      <c r="A154" t="s">
-        <v>164</v>
+      <c r="A154">
+        <v>1.664045875650331E+18</v>
       </c>
       <c r="B154" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>371</v>
+        <v>168</v>
       </c>
       <c r="D154" t="s">
-        <v>530</v>
+        <v>327</v>
       </c>
       <c r="E154">
         <v>0</v>
@@ -8150,21 +7541,21 @@
         <v>3198</v>
       </c>
       <c r="K154" t="s">
-        <v>681</v>
+        <v>478</v>
       </c>
     </row>
     <row r="155" spans="1:11">
-      <c r="A155" t="s">
-        <v>165</v>
+      <c r="A155">
+        <v>1.664023601756897E+18</v>
       </c>
       <c r="B155" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>372</v>
+        <v>169</v>
       </c>
       <c r="D155" t="s">
-        <v>531</v>
+        <v>328</v>
       </c>
       <c r="E155">
         <v>1037</v>
@@ -8185,33 +7576,33 @@
         <v>50477</v>
       </c>
       <c r="K155" t="s">
-        <v>682</v>
+        <v>479</v>
       </c>
     </row>
     <row r="156" spans="1:11">
-      <c r="A156" t="s">
-        <v>166</v>
+      <c r="A156">
+        <v>1.663879826623611E+18</v>
       </c>
       <c r="B156" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>373</v>
+        <v>170</v>
       </c>
       <c r="D156" t="s">
-        <v>532</v>
+        <v>329</v>
       </c>
       <c r="E156">
-        <v>0</v>
+        <v>433</v>
       </c>
       <c r="F156">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="G156">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="H156">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I156">
         <v>0</v>
@@ -8220,21 +7611,21 @@
         <v>44218</v>
       </c>
       <c r="K156" t="s">
-        <v>683</v>
+        <v>480</v>
       </c>
     </row>
     <row r="157" spans="1:11">
-      <c r="A157" t="s">
-        <v>167</v>
+      <c r="A157">
+        <v>1.663878777707848E+18</v>
       </c>
       <c r="B157" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>374</v>
+        <v>171</v>
       </c>
       <c r="D157" t="s">
-        <v>533</v>
+        <v>330</v>
       </c>
       <c r="E157">
         <v>0</v>
@@ -8255,21 +7646,21 @@
         <v>197806</v>
       </c>
       <c r="K157" t="s">
-        <v>684</v>
+        <v>481</v>
       </c>
     </row>
     <row r="158" spans="1:11">
-      <c r="A158" t="s">
-        <v>168</v>
+      <c r="A158">
+        <v>1.663864642567918E+18</v>
       </c>
       <c r="B158" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>375</v>
+        <v>172</v>
       </c>
       <c r="D158" t="s">
-        <v>534</v>
+        <v>331</v>
       </c>
       <c r="E158">
         <v>53</v>
@@ -8290,21 +7681,21 @@
         <v>5969</v>
       </c>
       <c r="K158" t="s">
-        <v>685</v>
+        <v>482</v>
       </c>
     </row>
     <row r="159" spans="1:11">
-      <c r="A159" t="s">
-        <v>169</v>
+      <c r="A159">
+        <v>1.663863231159345E+18</v>
       </c>
       <c r="B159" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>376</v>
+        <v>173</v>
       </c>
       <c r="D159" t="s">
-        <v>535</v>
+        <v>332</v>
       </c>
       <c r="E159">
         <v>161</v>
@@ -8325,21 +7716,21 @@
         <v>14193</v>
       </c>
       <c r="K159" t="s">
-        <v>686</v>
+        <v>483</v>
       </c>
     </row>
     <row r="160" spans="1:11">
-      <c r="A160" t="s">
-        <v>170</v>
+      <c r="A160">
+        <v>1.663849151526851E+18</v>
       </c>
       <c r="B160" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>377</v>
+        <v>174</v>
       </c>
       <c r="D160" t="s">
-        <v>536</v>
+        <v>333</v>
       </c>
       <c r="E160">
         <v>48</v>
@@ -8360,21 +7751,21 @@
         <v>4944</v>
       </c>
       <c r="K160" t="s">
-        <v>687</v>
+        <v>484</v>
       </c>
     </row>
     <row r="161" spans="1:11">
-      <c r="A161" t="s">
-        <v>171</v>
+      <c r="A161">
+        <v>1.663681443803931E+18</v>
       </c>
       <c r="B161" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>378</v>
+        <v>175</v>
       </c>
       <c r="D161" t="s">
-        <v>537</v>
+        <v>334</v>
       </c>
       <c r="E161">
         <v>0</v>
@@ -8395,21 +7786,21 @@
         <v>37084</v>
       </c>
       <c r="K161" t="s">
-        <v>688</v>
+        <v>485</v>
       </c>
     </row>
     <row r="162" spans="1:11">
-      <c r="A162" t="s">
-        <v>172</v>
+      <c r="A162">
+        <v>1.652792458181263E+18</v>
       </c>
       <c r="B162" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>379</v>
+        <v>176</v>
       </c>
       <c r="D162" t="s">
-        <v>538</v>
+        <v>335</v>
       </c>
       <c r="E162">
         <v>0</v>
@@ -8430,21 +7821,21 @@
         <v>226902</v>
       </c>
       <c r="K162" t="s">
-        <v>689</v>
+        <v>486</v>
       </c>
     </row>
     <row r="163" spans="1:11">
-      <c r="A163" t="s">
-        <v>173</v>
+      <c r="A163">
+        <v>1.65278943044318E+18</v>
       </c>
       <c r="B163" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>380</v>
+        <v>177</v>
       </c>
       <c r="D163" t="s">
-        <v>539</v>
+        <v>336</v>
       </c>
       <c r="E163">
         <v>0</v>
@@ -8465,21 +7856,21 @@
         <v>47927</v>
       </c>
       <c r="K163" t="s">
-        <v>690</v>
+        <v>487</v>
       </c>
     </row>
     <row r="164" spans="1:11">
-      <c r="A164" t="s">
-        <v>174</v>
+      <c r="A164">
+        <v>1.652786591478194E+18</v>
       </c>
       <c r="B164" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>381</v>
+        <v>178</v>
       </c>
       <c r="D164" t="s">
-        <v>540</v>
+        <v>337</v>
       </c>
       <c r="E164">
         <v>107</v>
@@ -8500,21 +7891,21 @@
         <v>20127</v>
       </c>
       <c r="K164" t="s">
-        <v>691</v>
+        <v>488</v>
       </c>
     </row>
     <row r="165" spans="1:11">
-      <c r="A165" t="s">
-        <v>175</v>
+      <c r="A165">
+        <v>1.652778262702039E+18</v>
       </c>
       <c r="B165" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>382</v>
+        <v>179</v>
       </c>
       <c r="D165" t="s">
-        <v>541</v>
+        <v>338</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -8535,21 +7926,21 @@
         <v>19564</v>
       </c>
       <c r="K165" t="s">
-        <v>692</v>
+        <v>489</v>
       </c>
     </row>
     <row r="166" spans="1:11">
-      <c r="A166" t="s">
-        <v>176</v>
+      <c r="A166">
+        <v>1.652775309014446E+18</v>
       </c>
       <c r="B166" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>383</v>
+        <v>180</v>
       </c>
       <c r="D166" t="s">
-        <v>542</v>
+        <v>339</v>
       </c>
       <c r="E166">
         <v>0</v>
@@ -8570,21 +7961,21 @@
         <v>48070</v>
       </c>
       <c r="K166" t="s">
-        <v>693</v>
+        <v>490</v>
       </c>
     </row>
     <row r="167" spans="1:11">
-      <c r="A167" t="s">
-        <v>177</v>
+      <c r="A167">
+        <v>1.652759568479588E+18</v>
       </c>
       <c r="B167" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>384</v>
+        <v>181</v>
       </c>
       <c r="D167" t="s">
-        <v>543</v>
+        <v>340</v>
       </c>
       <c r="E167">
         <v>103</v>
@@ -8605,21 +7996,21 @@
         <v>21040</v>
       </c>
       <c r="K167" t="s">
-        <v>694</v>
+        <v>491</v>
       </c>
     </row>
     <row r="168" spans="1:11">
-      <c r="A168" t="s">
-        <v>178</v>
+      <c r="A168">
+        <v>1.652758073541292E+18</v>
       </c>
       <c r="B168" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>385</v>
+        <v>182</v>
       </c>
       <c r="D168" t="s">
-        <v>544</v>
+        <v>341</v>
       </c>
       <c r="E168">
         <v>0</v>
@@ -8640,21 +8031,21 @@
         <v>174717</v>
       </c>
       <c r="K168" t="s">
-        <v>695</v>
+        <v>492</v>
       </c>
     </row>
     <row r="169" spans="1:11">
-      <c r="A169" t="s">
-        <v>179</v>
+      <c r="A169">
+        <v>1.652730128177279E+18</v>
       </c>
       <c r="B169" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>386</v>
+        <v>183</v>
       </c>
       <c r="D169" t="s">
-        <v>545</v>
+        <v>342</v>
       </c>
       <c r="E169">
         <v>0</v>
@@ -8675,21 +8066,21 @@
         <v>113382</v>
       </c>
       <c r="K169" t="s">
-        <v>696</v>
+        <v>493</v>
       </c>
     </row>
     <row r="170" spans="1:11">
-      <c r="A170" t="s">
-        <v>180</v>
+      <c r="A170">
+        <v>1.652653921628824E+18</v>
       </c>
       <c r="B170" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>387</v>
+        <v>184</v>
       </c>
       <c r="D170" t="s">
-        <v>544</v>
+        <v>341</v>
       </c>
       <c r="E170">
         <v>0</v>
@@ -8710,21 +8101,21 @@
         <v>174717</v>
       </c>
       <c r="K170" t="s">
-        <v>695</v>
+        <v>492</v>
       </c>
     </row>
     <row r="171" spans="1:11">
-      <c r="A171" t="s">
-        <v>181</v>
+      <c r="A171">
+        <v>1.65263783204379E+18</v>
       </c>
       <c r="B171" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>388</v>
+        <v>185</v>
       </c>
       <c r="D171" t="s">
-        <v>546</v>
+        <v>343</v>
       </c>
       <c r="E171">
         <v>0</v>
@@ -8745,21 +8136,21 @@
         <v>239804</v>
       </c>
       <c r="K171" t="s">
-        <v>697</v>
+        <v>494</v>
       </c>
     </row>
     <row r="172" spans="1:11">
-      <c r="A172" t="s">
-        <v>182</v>
+      <c r="A172">
+        <v>1.652632250100351E+18</v>
       </c>
       <c r="B172" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>389</v>
+        <v>186</v>
       </c>
       <c r="D172" t="s">
-        <v>547</v>
+        <v>344</v>
       </c>
       <c r="E172">
         <v>112</v>
@@ -8780,21 +8171,21 @@
         <v>13536</v>
       </c>
       <c r="K172" t="s">
-        <v>698</v>
+        <v>495</v>
       </c>
     </row>
     <row r="173" spans="1:11">
-      <c r="A173" t="s">
-        <v>183</v>
+      <c r="A173">
+        <v>1.652613708361736E+18</v>
       </c>
       <c r="B173" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>390</v>
+        <v>187</v>
       </c>
       <c r="D173" t="s">
-        <v>544</v>
+        <v>341</v>
       </c>
       <c r="E173">
         <v>0</v>
@@ -8815,21 +8206,21 @@
         <v>174717</v>
       </c>
       <c r="K173" t="s">
-        <v>695</v>
+        <v>492</v>
       </c>
     </row>
     <row r="174" spans="1:11">
-      <c r="A174" t="s">
-        <v>184</v>
+      <c r="A174">
+        <v>1.652613172400988E+18</v>
       </c>
       <c r="B174" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>391</v>
+        <v>188</v>
       </c>
       <c r="D174" t="s">
-        <v>544</v>
+        <v>341</v>
       </c>
       <c r="E174">
         <v>0</v>
@@ -8850,21 +8241,21 @@
         <v>174717</v>
       </c>
       <c r="K174" t="s">
-        <v>695</v>
+        <v>492</v>
       </c>
     </row>
     <row r="175" spans="1:11">
-      <c r="A175" t="s">
-        <v>185</v>
+      <c r="A175">
+        <v>1.652611840378126E+18</v>
       </c>
       <c r="B175" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>392</v>
+        <v>189</v>
       </c>
       <c r="D175" t="s">
-        <v>548</v>
+        <v>345</v>
       </c>
       <c r="E175">
         <v>114</v>
@@ -8885,21 +8276,21 @@
         <v>24445</v>
       </c>
       <c r="K175" t="s">
-        <v>699</v>
+        <v>496</v>
       </c>
     </row>
     <row r="176" spans="1:11">
-      <c r="A176" t="s">
-        <v>186</v>
+      <c r="A176">
+        <v>1.652610742292562E+18</v>
       </c>
       <c r="B176" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>393</v>
+        <v>190</v>
       </c>
       <c r="D176" t="s">
-        <v>544</v>
+        <v>341</v>
       </c>
       <c r="E176">
         <v>0</v>
@@ -8920,21 +8311,21 @@
         <v>174717</v>
       </c>
       <c r="K176" t="s">
-        <v>695</v>
+        <v>492</v>
       </c>
     </row>
     <row r="177" spans="1:11">
-      <c r="A177" t="s">
-        <v>187</v>
+      <c r="A177">
+        <v>1.652610743580217E+18</v>
       </c>
       <c r="B177" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>394</v>
+        <v>191</v>
       </c>
       <c r="D177" t="s">
-        <v>544</v>
+        <v>341</v>
       </c>
       <c r="E177">
         <v>0</v>
@@ -8955,21 +8346,21 @@
         <v>174717</v>
       </c>
       <c r="K177" t="s">
-        <v>695</v>
+        <v>492</v>
       </c>
     </row>
     <row r="178" spans="1:11">
-      <c r="A178" t="s">
-        <v>188</v>
+      <c r="A178">
+        <v>1.652607935829123E+18</v>
       </c>
       <c r="B178" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>395</v>
+        <v>192</v>
       </c>
       <c r="D178" t="s">
-        <v>549</v>
+        <v>346</v>
       </c>
       <c r="E178">
         <v>580</v>
@@ -8990,21 +8381,21 @@
         <v>248225</v>
       </c>
       <c r="K178" t="s">
-        <v>700</v>
+        <v>497</v>
       </c>
     </row>
     <row r="179" spans="1:11">
-      <c r="A179" t="s">
-        <v>189</v>
+      <c r="A179">
+        <v>1.652606997215183E+18</v>
       </c>
       <c r="B179" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>396</v>
+        <v>193</v>
       </c>
       <c r="D179" t="s">
-        <v>550</v>
+        <v>347</v>
       </c>
       <c r="E179">
         <v>210</v>
@@ -9025,21 +8416,21 @@
         <v>23707</v>
       </c>
       <c r="K179" t="s">
-        <v>701</v>
+        <v>498</v>
       </c>
     </row>
     <row r="180" spans="1:11">
-      <c r="A180" t="s">
-        <v>190</v>
+      <c r="A180">
+        <v>1.652605299235119E+18</v>
       </c>
       <c r="B180" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>397</v>
+        <v>194</v>
       </c>
       <c r="D180" t="s">
-        <v>551</v>
+        <v>348</v>
       </c>
       <c r="E180">
         <v>0</v>
@@ -9060,21 +8451,21 @@
         <v>803077</v>
       </c>
       <c r="K180" t="s">
-        <v>702</v>
+        <v>499</v>
       </c>
     </row>
     <row r="181" spans="1:11">
-      <c r="A181" t="s">
-        <v>191</v>
+      <c r="A181">
+        <v>1.65260481488957E+18</v>
       </c>
       <c r="B181" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>398</v>
+        <v>195</v>
       </c>
       <c r="D181" t="s">
-        <v>551</v>
+        <v>348</v>
       </c>
       <c r="E181">
         <v>0</v>
@@ -9095,21 +8486,21 @@
         <v>803077</v>
       </c>
       <c r="K181" t="s">
-        <v>702</v>
+        <v>499</v>
       </c>
     </row>
     <row r="182" spans="1:11">
-      <c r="A182" t="s">
-        <v>192</v>
+      <c r="A182">
+        <v>1.652603868771938E+18</v>
       </c>
       <c r="B182" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>399</v>
+        <v>196</v>
       </c>
       <c r="D182" t="s">
-        <v>552</v>
+        <v>349</v>
       </c>
       <c r="E182">
         <v>746</v>
@@ -9130,21 +8521,21 @@
         <v>197186</v>
       </c>
       <c r="K182" t="s">
-        <v>703</v>
+        <v>500</v>
       </c>
     </row>
     <row r="183" spans="1:11">
-      <c r="A183" t="s">
-        <v>193</v>
+      <c r="A183">
+        <v>1.652600422668829E+18</v>
       </c>
       <c r="B183" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>400</v>
+        <v>197</v>
       </c>
       <c r="D183" t="s">
-        <v>553</v>
+        <v>350</v>
       </c>
       <c r="E183">
         <v>114</v>
@@ -9165,21 +8556,21 @@
         <v>13770</v>
       </c>
       <c r="K183" t="s">
-        <v>704</v>
+        <v>501</v>
       </c>
     </row>
     <row r="184" spans="1:11">
-      <c r="A184" t="s">
-        <v>194</v>
+      <c r="A184">
+        <v>1.652597521510744E+18</v>
       </c>
       <c r="B184" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>401</v>
+        <v>198</v>
       </c>
       <c r="D184" t="s">
-        <v>554</v>
+        <v>351</v>
       </c>
       <c r="E184">
         <v>176</v>
@@ -9200,21 +8591,21 @@
         <v>103883</v>
       </c>
       <c r="K184" t="s">
-        <v>705</v>
+        <v>502</v>
       </c>
     </row>
     <row r="185" spans="1:11">
-      <c r="A185" t="s">
-        <v>195</v>
+      <c r="A185">
+        <v>1.641887533855396E+18</v>
       </c>
       <c r="B185" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>402</v>
+        <v>199</v>
       </c>
       <c r="D185" t="s">
-        <v>555</v>
+        <v>352</v>
       </c>
       <c r="E185">
         <v>70</v>
@@ -9235,21 +8626,21 @@
         <v>35206</v>
       </c>
       <c r="K185" t="s">
-        <v>706</v>
+        <v>503</v>
       </c>
     </row>
     <row r="186" spans="1:11">
-      <c r="A186" t="s">
-        <v>196</v>
+      <c r="A186">
+        <v>1.641855732931756E+18</v>
       </c>
       <c r="B186" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="D186" t="s">
-        <v>556</v>
+        <v>353</v>
       </c>
       <c r="E186">
         <v>396</v>
@@ -9270,21 +8661,21 @@
         <v>26351</v>
       </c>
       <c r="K186" t="s">
-        <v>707</v>
+        <v>504</v>
       </c>
     </row>
     <row r="187" spans="1:11">
-      <c r="A187" t="s">
-        <v>197</v>
+      <c r="A187">
+        <v>1.641800899814121E+18</v>
       </c>
       <c r="B187" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>404</v>
+        <v>201</v>
       </c>
       <c r="D187" t="s">
-        <v>557</v>
+        <v>354</v>
       </c>
       <c r="E187">
         <v>45</v>
@@ -9305,21 +8696,21 @@
         <v>5144</v>
       </c>
       <c r="K187" t="s">
-        <v>708</v>
+        <v>505</v>
       </c>
     </row>
     <row r="188" spans="1:11">
-      <c r="A188" t="s">
-        <v>198</v>
+      <c r="A188">
+        <v>1.641792600863646E+18</v>
       </c>
       <c r="B188" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>405</v>
+        <v>202</v>
       </c>
       <c r="D188" t="s">
-        <v>558</v>
+        <v>355</v>
       </c>
       <c r="E188">
         <v>26</v>
@@ -9340,21 +8731,21 @@
         <v>4629</v>
       </c>
       <c r="K188" t="s">
-        <v>709</v>
+        <v>506</v>
       </c>
     </row>
     <row r="189" spans="1:11">
-      <c r="A189" t="s">
-        <v>199</v>
+      <c r="A189">
+        <v>1.64178721005466E+18</v>
       </c>
       <c r="B189" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>406</v>
+        <v>203</v>
       </c>
       <c r="D189" t="s">
-        <v>559</v>
+        <v>356</v>
       </c>
       <c r="E189">
         <v>50</v>
@@ -9375,30 +8766,30 @@
         <v>12742</v>
       </c>
       <c r="K189" t="s">
-        <v>710</v>
+        <v>507</v>
       </c>
     </row>
     <row r="190" spans="1:11">
-      <c r="A190" t="s">
-        <v>200</v>
+      <c r="A190">
+        <v>1.641780775753269E+18</v>
       </c>
       <c r="B190" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>407</v>
+        <v>204</v>
       </c>
       <c r="D190" t="s">
-        <v>560</v>
+        <v>357</v>
       </c>
       <c r="E190">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="F190">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G190">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H190">
         <v>0</v>
@@ -9410,21 +8801,21 @@
         <v>9699</v>
       </c>
       <c r="K190" t="s">
-        <v>711</v>
+        <v>508</v>
       </c>
     </row>
     <row r="191" spans="1:11">
-      <c r="A191" t="s">
-        <v>201</v>
+      <c r="A191">
+        <v>1.641780741360026E+18</v>
       </c>
       <c r="B191" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>408</v>
+        <v>205</v>
       </c>
       <c r="D191" t="s">
-        <v>560</v>
+        <v>357</v>
       </c>
       <c r="E191">
         <v>59</v>
@@ -9445,21 +8836,21 @@
         <v>9699</v>
       </c>
       <c r="K191" t="s">
-        <v>711</v>
+        <v>508</v>
       </c>
     </row>
     <row r="192" spans="1:11">
-      <c r="A192" t="s">
-        <v>202</v>
+      <c r="A192">
+        <v>1.641776275877507E+18</v>
       </c>
       <c r="B192" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>409</v>
+        <v>206</v>
       </c>
       <c r="D192" t="s">
-        <v>561</v>
+        <v>358</v>
       </c>
       <c r="E192">
         <v>457</v>
@@ -9480,21 +8871,21 @@
         <v>43972</v>
       </c>
       <c r="K192" t="s">
-        <v>712</v>
+        <v>509</v>
       </c>
     </row>
     <row r="193" spans="1:11">
-      <c r="A193" t="s">
-        <v>203</v>
+      <c r="A193">
+        <v>1.641760900993495E+18</v>
       </c>
       <c r="B193" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>410</v>
+        <v>207</v>
       </c>
       <c r="D193" t="s">
-        <v>562</v>
+        <v>359</v>
       </c>
       <c r="E193">
         <v>0</v>
@@ -9515,21 +8906,21 @@
         <v>37842</v>
       </c>
       <c r="K193" t="s">
-        <v>713</v>
+        <v>510</v>
       </c>
     </row>
     <row r="194" spans="1:11">
-      <c r="A194" t="s">
-        <v>204</v>
+      <c r="A194">
+        <v>1.619650876221829E+18</v>
       </c>
       <c r="B194" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>411</v>
+        <v>208</v>
       </c>
       <c r="D194" t="s">
-        <v>563</v>
+        <v>360</v>
       </c>
       <c r="E194">
         <v>480</v>
@@ -9550,21 +8941,21 @@
         <v>73008</v>
       </c>
       <c r="K194" t="s">
-        <v>714</v>
+        <v>511</v>
       </c>
     </row>
     <row r="195" spans="1:11">
-      <c r="A195" t="s">
-        <v>205</v>
+      <c r="A195">
+        <v>1.620358713474433E+18</v>
       </c>
       <c r="B195" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>412</v>
+        <v>209</v>
       </c>
       <c r="D195" t="s">
-        <v>564</v>
+        <v>361</v>
       </c>
       <c r="E195">
         <v>61</v>
@@ -9585,21 +8976,21 @@
         <v>7773</v>
       </c>
       <c r="K195" t="s">
-        <v>715</v>
+        <v>512</v>
       </c>
     </row>
     <row r="196" spans="1:11">
-      <c r="A196" t="s">
-        <v>206</v>
+      <c r="A196">
+        <v>1.664037638863454E+18</v>
       </c>
       <c r="B196" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>413</v>
+        <v>210</v>
       </c>
       <c r="D196" t="s">
-        <v>565</v>
+        <v>362</v>
       </c>
       <c r="E196">
         <v>85</v>
@@ -9620,21 +9011,21 @@
         <v>5677</v>
       </c>
       <c r="K196" t="s">
-        <v>716</v>
+        <v>513</v>
       </c>
     </row>
     <row r="197" spans="1:11">
-      <c r="A197" t="s">
-        <v>207</v>
+      <c r="A197">
+        <v>1.663858197310865E+18</v>
       </c>
       <c r="B197" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>414</v>
+        <v>211</v>
       </c>
       <c r="D197" t="s">
-        <v>566</v>
+        <v>363</v>
       </c>
       <c r="E197">
         <v>45</v>
@@ -9655,21 +9046,21 @@
         <v>4880</v>
       </c>
       <c r="K197" t="s">
-        <v>717</v>
+        <v>514</v>
       </c>
     </row>
     <row r="198" spans="1:11">
-      <c r="A198" t="s">
-        <v>208</v>
+      <c r="A198">
+        <v>1.663852815511429E+18</v>
       </c>
       <c r="B198" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>415</v>
+        <v>212</v>
       </c>
       <c r="D198" t="s">
-        <v>567</v>
+        <v>364</v>
       </c>
       <c r="E198">
         <v>86</v>
@@ -9690,21 +9081,21 @@
         <v>15082</v>
       </c>
       <c r="K198" t="s">
-        <v>718</v>
+        <v>515</v>
       </c>
     </row>
     <row r="199" spans="1:11">
-      <c r="A199" t="s">
-        <v>209</v>
+      <c r="A199">
+        <v>1.663817389069283E+18</v>
       </c>
       <c r="B199" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>416</v>
+        <v>213</v>
       </c>
       <c r="D199" t="s">
-        <v>568</v>
+        <v>365</v>
       </c>
       <c r="E199">
         <v>111</v>
@@ -9725,21 +9116,21 @@
         <v>11918</v>
       </c>
       <c r="K199" t="s">
-        <v>719</v>
+        <v>516</v>
       </c>
     </row>
     <row r="200" spans="1:11">
-      <c r="A200" t="s">
-        <v>210</v>
+      <c r="A200">
+        <v>1.652613288054727E+18</v>
       </c>
       <c r="B200" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>417</v>
+        <v>214</v>
       </c>
       <c r="D200" t="s">
-        <v>544</v>
+        <v>341</v>
       </c>
       <c r="E200">
         <v>0</v>
@@ -9760,21 +9151,21 @@
         <v>174718</v>
       </c>
       <c r="K200" t="s">
-        <v>695</v>
+        <v>492</v>
       </c>
     </row>
     <row r="201" spans="1:11">
-      <c r="A201" t="s">
-        <v>211</v>
+      <c r="A201">
+        <v>1.652599667190907E+18</v>
       </c>
       <c r="B201" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>418</v>
+        <v>215</v>
       </c>
       <c r="D201" t="s">
-        <v>569</v>
+        <v>366</v>
       </c>
       <c r="E201">
         <v>0</v>
@@ -9795,21 +9186,21 @@
         <v>479249</v>
       </c>
       <c r="K201" t="s">
-        <v>720</v>
+        <v>517</v>
       </c>
     </row>
     <row r="202" spans="1:11">
-      <c r="A202" t="s">
-        <v>212</v>
+      <c r="A202">
+        <v>1.641796973115187E+18</v>
       </c>
       <c r="B202" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>419</v>
+        <v>216</v>
       </c>
       <c r="D202" t="s">
-        <v>570</v>
+        <v>367</v>
       </c>
       <c r="E202">
         <v>57</v>
@@ -9830,21 +9221,21 @@
         <v>6856</v>
       </c>
       <c r="K202" t="s">
-        <v>721</v>
+        <v>518</v>
       </c>
     </row>
     <row r="203" spans="1:11">
-      <c r="A203" t="s">
-        <v>213</v>
+      <c r="A203">
+        <v>1.641778203978088E+18</v>
       </c>
       <c r="B203" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>420</v>
+        <v>217</v>
       </c>
       <c r="D203" t="s">
-        <v>571</v>
+        <v>368</v>
       </c>
       <c r="E203">
         <v>33</v>
@@ -9865,21 +9256,21 @@
         <v>3930</v>
       </c>
       <c r="K203" t="s">
-        <v>722</v>
+        <v>519</v>
       </c>
     </row>
     <row r="204" spans="1:11">
-      <c r="A204" t="s">
-        <v>214</v>
+      <c r="A204">
+        <v>1.619731584768442E+18</v>
       </c>
       <c r="B204" t="s">
+        <v>15</v>
+      </c>
+      <c r="C204" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="C204" s="2" t="s">
-        <v>421</v>
-      </c>
       <c r="D204" t="s">
-        <v>572</v>
+        <v>369</v>
       </c>
       <c r="E204">
         <v>102</v>
@@ -9900,7 +9291,7 @@
         <v>23817</v>
       </c>
       <c r="K204" t="s">
-        <v>723</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>
